--- a/ig/mc-add-profils-dp/StructureDefinition-as-dp-organization.xlsx
+++ b/ig/mc-add-profils-dp/StructureDefinition-as-dp-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-17T18:21:34+00:00</t>
+    <t>2023-05-17T18:27:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/mc-add-profils-dp/StructureDefinition-as-dp-organization.xlsx
+++ b/ig/mc-add-profils-dp/StructureDefinition-as-dp-organization.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AJ$152</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AJ$156</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4923" uniqueCount="625">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5049" uniqueCount="627">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-17T18:27:08+00:00</t>
+    <t>2023-05-23T08:43:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -78,7 +78,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Profil créé à partir de as-organization  dans le contexte des données en libre accès.</t>
+    <t>Profil applicatif créé à partir du profil générique as-organization  dans le contexte des données en libre accès de l’Annuaire Santé.</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -1413,6 +1413,24 @@
     <t>ContactPoint.period</t>
   </si>
   <si>
+    <t>Organization.telecom.period.id</t>
+  </si>
+  <si>
+    <t>Organization.telecom.period.extension</t>
+  </si>
+  <si>
+    <t>Organization.telecom.period.start</t>
+  </si>
+  <si>
+    <t>Starting time with inclusive boundary</t>
+  </si>
+  <si>
+    <t>Organization.telecom.period.end</t>
+  </si>
+  <si>
+    <t>End time with inclusive boundary, if not ongoing</t>
+  </si>
+  <si>
     <t>Organization.address</t>
   </si>
   <si>
@@ -1769,12 +1787,6 @@
     <t>responsible</t>
   </si>
   <si>
-    <t>[DR] : responsable de la BAL MSS.</t>
-  </si>
-  <si>
-    <t>Synonyme : mailBoxMSSresponsable</t>
-  </si>
-  <si>
     <t>Organization.contact.telecom:mailbox-mss.extension:as-mailbox-mss-metadata.extension:responsible.id</t>
   </si>
   <si>
@@ -1815,12 +1827,6 @@
   </si>
   <si>
     <t>phone</t>
-  </si>
-  <si>
-    <t>[DR] : Coordonnées téléphoniques spécifiques à l’usage de la BAL MSS.</t>
-  </si>
-  <si>
-    <t>Synonyme : mailBoxMSS.phone</t>
   </si>
   <si>
     <t>Organization.contact.telecom:mailbox-mss.extension:as-mailbox-mss-metadata.extension:phone.id</t>
@@ -2284,7 +2290,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AJ152"/>
+  <dimension ref="A1:AJ156"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="118.80859375" customWidth="true" bestFit="true"/>
@@ -11076,10 +11082,10 @@
         <v>72</v>
       </c>
       <c r="G86" t="s" s="2">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="H86" t="s" s="2">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="I86" t="s" s="2">
         <v>71</v>
@@ -11088,20 +11094,16 @@
         <v>71</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>446</v>
+        <v>146</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>447</v>
+        <v>147</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>448</v>
-      </c>
-      <c r="N86" t="s" s="2">
-        <v>449</v>
-      </c>
-      <c r="O86" t="s" s="2">
-        <v>450</v>
-      </c>
+        <v>148</v>
+      </c>
+      <c r="N86" s="2"/>
+      <c r="O86" s="2"/>
       <c r="P86" t="s" s="2">
         <v>71</v>
       </c>
@@ -11149,38 +11151,38 @@
         <v>71</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>445</v>
+        <v>149</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AH86" t="s" s="2">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="AI86" t="s" s="2">
-        <v>90</v>
+        <v>71</v>
       </c>
       <c r="AJ86" t="s" s="2">
-        <v>451</v>
+        <v>71</v>
       </c>
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>452</v>
+        <v>446</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>452</v>
+        <v>446</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
-        <v>71</v>
+        <v>122</v>
       </c>
       <c r="E87" s="2"/>
       <c r="F87" t="s" s="2">
         <v>72</v>
       </c>
       <c r="G87" t="s" s="2">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="H87" t="s" s="2">
         <v>71</v>
@@ -11189,23 +11191,21 @@
         <v>71</v>
       </c>
       <c r="J87" t="s" s="2">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>453</v>
+        <v>123</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>454</v>
+        <v>124</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>455</v>
+        <v>152</v>
       </c>
       <c r="N87" t="s" s="2">
-        <v>456</v>
-      </c>
-      <c r="O87" t="s" s="2">
-        <v>457</v>
-      </c>
+        <v>126</v>
+      </c>
+      <c r="O87" s="2"/>
       <c r="P87" t="s" s="2">
         <v>71</v>
       </c>
@@ -11241,39 +11241,39 @@
         <v>71</v>
       </c>
       <c r="AB87" t="s" s="2">
-        <v>71</v>
+        <v>127</v>
       </c>
       <c r="AC87" t="s" s="2">
-        <v>71</v>
+        <v>128</v>
       </c>
       <c r="AD87" t="s" s="2">
         <v>71</v>
       </c>
       <c r="AE87" t="s" s="2">
-        <v>71</v>
+        <v>129</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>452</v>
+        <v>153</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AH87" t="s" s="2">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="AI87" t="s" s="2">
         <v>90</v>
       </c>
       <c r="AJ87" t="s" s="2">
-        <v>260</v>
+        <v>131</v>
       </c>
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>458</v>
+        <v>447</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>458</v>
+        <v>447</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -11284,7 +11284,7 @@
         <v>72</v>
       </c>
       <c r="G88" t="s" s="2">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="H88" t="s" s="2">
         <v>71</v>
@@ -11293,18 +11293,20 @@
         <v>71</v>
       </c>
       <c r="J88" t="s" s="2">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>146</v>
+        <v>177</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>147</v>
+        <v>448</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>148</v>
-      </c>
-      <c r="N88" s="2"/>
+        <v>179</v>
+      </c>
+      <c r="N88" t="s" s="2">
+        <v>180</v>
+      </c>
       <c r="O88" s="2"/>
       <c r="P88" t="s" s="2">
         <v>71</v>
@@ -11353,7 +11355,7 @@
         <v>71</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>149</v>
+        <v>181</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>72</v>
@@ -11362,29 +11364,29 @@
         <v>78</v>
       </c>
       <c r="AI88" t="s" s="2">
-        <v>71</v>
+        <v>182</v>
       </c>
       <c r="AJ88" t="s" s="2">
-        <v>71</v>
+        <v>91</v>
       </c>
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>459</v>
+        <v>449</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>459</v>
+        <v>449</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
-        <v>122</v>
+        <v>71</v>
       </c>
       <c r="E89" s="2"/>
       <c r="F89" t="s" s="2">
         <v>72</v>
       </c>
       <c r="G89" t="s" s="2">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="H89" t="s" s="2">
         <v>71</v>
@@ -11393,25 +11395,27 @@
         <v>71</v>
       </c>
       <c r="J89" t="s" s="2">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>123</v>
+        <v>177</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>124</v>
+        <v>450</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>152</v>
+        <v>186</v>
       </c>
       <c r="N89" t="s" s="2">
-        <v>126</v>
+        <v>187</v>
       </c>
       <c r="O89" s="2"/>
       <c r="P89" t="s" s="2">
         <v>71</v>
       </c>
-      <c r="Q89" s="2"/>
+      <c r="Q89" t="s" s="2">
+        <v>188</v>
+      </c>
       <c r="R89" t="s" s="2">
         <v>71</v>
       </c>
@@ -11443,39 +11447,39 @@
         <v>71</v>
       </c>
       <c r="AB89" t="s" s="2">
-        <v>127</v>
+        <v>71</v>
       </c>
       <c r="AC89" t="s" s="2">
-        <v>128</v>
+        <v>71</v>
       </c>
       <c r="AD89" t="s" s="2">
         <v>71</v>
       </c>
       <c r="AE89" t="s" s="2">
-        <v>129</v>
+        <v>71</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>153</v>
+        <v>189</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AH89" t="s" s="2">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="AI89" t="s" s="2">
-        <v>90</v>
+        <v>182</v>
       </c>
       <c r="AJ89" t="s" s="2">
-        <v>131</v>
+        <v>91</v>
       </c>
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>460</v>
+        <v>451</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>460</v>
+        <v>451</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -11486,30 +11490,32 @@
         <v>72</v>
       </c>
       <c r="G90" t="s" s="2">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="H90" t="s" s="2">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="I90" t="s" s="2">
         <v>71</v>
       </c>
       <c r="J90" t="s" s="2">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>146</v>
+        <v>452</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>461</v>
+        <v>453</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>462</v>
+        <v>454</v>
       </c>
       <c r="N90" t="s" s="2">
-        <v>463</v>
-      </c>
-      <c r="O90" s="2"/>
+        <v>455</v>
+      </c>
+      <c r="O90" t="s" s="2">
+        <v>456</v>
+      </c>
       <c r="P90" t="s" s="2">
         <v>71</v>
       </c>
@@ -11557,27 +11563,27 @@
         <v>71</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>464</v>
+        <v>451</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AH90" t="s" s="2">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="AI90" t="s" s="2">
-        <v>465</v>
+        <v>90</v>
       </c>
       <c r="AJ90" t="s" s="2">
-        <v>91</v>
+        <v>457</v>
       </c>
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>466</v>
+        <v>458</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>466</v>
+        <v>458</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -11600,18 +11606,20 @@
         <v>79</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>93</v>
+        <v>459</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>467</v>
+        <v>460</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>468</v>
+        <v>461</v>
       </c>
       <c r="N91" t="s" s="2">
-        <v>469</v>
-      </c>
-      <c r="O91" s="2"/>
+        <v>462</v>
+      </c>
+      <c r="O91" t="s" s="2">
+        <v>463</v>
+      </c>
       <c r="P91" t="s" s="2">
         <v>71</v>
       </c>
@@ -11635,13 +11643,13 @@
         <v>71</v>
       </c>
       <c r="X91" t="s" s="2">
-        <v>230</v>
+        <v>71</v>
       </c>
       <c r="Y91" t="s" s="2">
-        <v>470</v>
+        <v>71</v>
       </c>
       <c r="Z91" t="s" s="2">
-        <v>281</v>
+        <v>71</v>
       </c>
       <c r="AA91" t="s" s="2">
         <v>71</v>
@@ -11659,7 +11667,7 @@
         <v>71</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>471</v>
+        <v>458</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>72</v>
@@ -11671,15 +11679,15 @@
         <v>90</v>
       </c>
       <c r="AJ91" t="s" s="2">
-        <v>91</v>
+        <v>260</v>
       </c>
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>472</v>
+        <v>464</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>472</v>
+        <v>464</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -11699,20 +11707,18 @@
         <v>71</v>
       </c>
       <c r="J92" t="s" s="2">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>207</v>
+        <v>146</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>473</v>
+        <v>147</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>474</v>
-      </c>
-      <c r="N92" t="s" s="2">
-        <v>475</v>
-      </c>
+        <v>148</v>
+      </c>
+      <c r="N92" s="2"/>
       <c r="O92" s="2"/>
       <c r="P92" t="s" s="2">
         <v>71</v>
@@ -11761,7 +11767,7 @@
         <v>71</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>476</v>
+        <v>149</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>72</v>
@@ -11770,29 +11776,29 @@
         <v>78</v>
       </c>
       <c r="AI92" t="s" s="2">
-        <v>90</v>
+        <v>71</v>
       </c>
       <c r="AJ92" t="s" s="2">
-        <v>91</v>
+        <v>71</v>
       </c>
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>477</v>
+        <v>465</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>477</v>
+        <v>465</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
-        <v>71</v>
+        <v>122</v>
       </c>
       <c r="E93" s="2"/>
       <c r="F93" t="s" s="2">
         <v>72</v>
       </c>
       <c r="G93" t="s" s="2">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="H93" t="s" s="2">
         <v>71</v>
@@ -11801,19 +11807,19 @@
         <v>71</v>
       </c>
       <c r="J93" t="s" s="2">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>146</v>
+        <v>123</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>478</v>
+        <v>124</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>479</v>
+        <v>152</v>
       </c>
       <c r="N93" t="s" s="2">
-        <v>480</v>
+        <v>126</v>
       </c>
       <c r="O93" s="2"/>
       <c r="P93" t="s" s="2">
@@ -11851,39 +11857,39 @@
         <v>71</v>
       </c>
       <c r="AB93" t="s" s="2">
-        <v>71</v>
+        <v>127</v>
       </c>
       <c r="AC93" t="s" s="2">
-        <v>71</v>
+        <v>128</v>
       </c>
       <c r="AD93" t="s" s="2">
         <v>71</v>
       </c>
       <c r="AE93" t="s" s="2">
-        <v>71</v>
+        <v>129</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>481</v>
+        <v>153</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AH93" t="s" s="2">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="AI93" t="s" s="2">
         <v>90</v>
       </c>
       <c r="AJ93" t="s" s="2">
-        <v>91</v>
+        <v>131</v>
       </c>
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>482</v>
+        <v>466</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>482</v>
+        <v>466</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -11894,32 +11900,30 @@
         <v>72</v>
       </c>
       <c r="G94" t="s" s="2">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="H94" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="I94" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="J94" t="s" s="2">
         <v>79</v>
       </c>
-      <c r="I94" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="J94" t="s" s="2">
-        <v>71</v>
-      </c>
       <c r="K94" t="s" s="2">
-        <v>483</v>
+        <v>146</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>484</v>
+        <v>467</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>485</v>
+        <v>468</v>
       </c>
       <c r="N94" t="s" s="2">
-        <v>486</v>
-      </c>
-      <c r="O94" t="s" s="2">
-        <v>487</v>
-      </c>
+        <v>469</v>
+      </c>
+      <c r="O94" s="2"/>
       <c r="P94" t="s" s="2">
         <v>71</v>
       </c>
@@ -11967,16 +11971,16 @@
         <v>71</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>482</v>
+        <v>470</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AH94" t="s" s="2">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="AI94" t="s" s="2">
-        <v>90</v>
+        <v>471</v>
       </c>
       <c r="AJ94" t="s" s="2">
         <v>91</v>
@@ -11984,10 +11988,10 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>488</v>
+        <v>472</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>488</v>
+        <v>472</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -12007,18 +12011,20 @@
         <v>71</v>
       </c>
       <c r="J95" t="s" s="2">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>146</v>
+        <v>93</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>147</v>
+        <v>473</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>148</v>
-      </c>
-      <c r="N95" s="2"/>
+        <v>474</v>
+      </c>
+      <c r="N95" t="s" s="2">
+        <v>475</v>
+      </c>
       <c r="O95" s="2"/>
       <c r="P95" t="s" s="2">
         <v>71</v>
@@ -12043,13 +12049,13 @@
         <v>71</v>
       </c>
       <c r="X95" t="s" s="2">
-        <v>71</v>
+        <v>230</v>
       </c>
       <c r="Y95" t="s" s="2">
-        <v>71</v>
+        <v>476</v>
       </c>
       <c r="Z95" t="s" s="2">
-        <v>71</v>
+        <v>281</v>
       </c>
       <c r="AA95" t="s" s="2">
         <v>71</v>
@@ -12067,7 +12073,7 @@
         <v>71</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>149</v>
+        <v>477</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>72</v>
@@ -12076,29 +12082,29 @@
         <v>78</v>
       </c>
       <c r="AI95" t="s" s="2">
-        <v>71</v>
+        <v>90</v>
       </c>
       <c r="AJ95" t="s" s="2">
-        <v>71</v>
+        <v>91</v>
       </c>
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>489</v>
+        <v>478</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>489</v>
+        <v>478</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
-        <v>122</v>
+        <v>71</v>
       </c>
       <c r="E96" s="2"/>
       <c r="F96" t="s" s="2">
         <v>72</v>
       </c>
       <c r="G96" t="s" s="2">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="H96" t="s" s="2">
         <v>71</v>
@@ -12107,19 +12113,19 @@
         <v>71</v>
       </c>
       <c r="J96" t="s" s="2">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>123</v>
+        <v>207</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>124</v>
+        <v>479</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>152</v>
+        <v>480</v>
       </c>
       <c r="N96" t="s" s="2">
-        <v>126</v>
+        <v>481</v>
       </c>
       <c r="O96" s="2"/>
       <c r="P96" t="s" s="2">
@@ -12157,75 +12163,73 @@
         <v>71</v>
       </c>
       <c r="AB96" t="s" s="2">
-        <v>127</v>
+        <v>71</v>
       </c>
       <c r="AC96" t="s" s="2">
-        <v>128</v>
+        <v>71</v>
       </c>
       <c r="AD96" t="s" s="2">
         <v>71</v>
       </c>
       <c r="AE96" t="s" s="2">
-        <v>129</v>
+        <v>71</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>153</v>
+        <v>482</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AH96" t="s" s="2">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="AI96" t="s" s="2">
         <v>90</v>
       </c>
       <c r="AJ96" t="s" s="2">
-        <v>131</v>
+        <v>91</v>
       </c>
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>490</v>
+        <v>483</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>490</v>
+        <v>483</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
-        <v>491</v>
+        <v>71</v>
       </c>
       <c r="E97" s="2"/>
       <c r="F97" t="s" s="2">
         <v>72</v>
       </c>
       <c r="G97" t="s" s="2">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="H97" t="s" s="2">
         <v>71</v>
       </c>
       <c r="I97" t="s" s="2">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="J97" t="s" s="2">
         <v>79</v>
       </c>
       <c r="K97" t="s" s="2">
-        <v>123</v>
+        <v>146</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>492</v>
+        <v>484</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>493</v>
+        <v>485</v>
       </c>
       <c r="N97" t="s" s="2">
-        <v>126</v>
-      </c>
-      <c r="O97" t="s" s="2">
-        <v>204</v>
-      </c>
+        <v>486</v>
+      </c>
+      <c r="O97" s="2"/>
       <c r="P97" t="s" s="2">
         <v>71</v>
       </c>
@@ -12273,27 +12277,27 @@
         <v>71</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>494</v>
+        <v>487</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AH97" t="s" s="2">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="AI97" t="s" s="2">
         <v>90</v>
       </c>
       <c r="AJ97" t="s" s="2">
-        <v>131</v>
+        <v>91</v>
       </c>
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>495</v>
+        <v>488</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>495</v>
+        <v>488</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -12304,10 +12308,10 @@
         <v>72</v>
       </c>
       <c r="G98" t="s" s="2">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="H98" t="s" s="2">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="I98" t="s" s="2">
         <v>71</v>
@@ -12316,19 +12320,19 @@
         <v>71</v>
       </c>
       <c r="K98" t="s" s="2">
-        <v>225</v>
+        <v>489</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>496</v>
+        <v>490</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>497</v>
+        <v>491</v>
       </c>
       <c r="N98" t="s" s="2">
-        <v>498</v>
+        <v>492</v>
       </c>
       <c r="O98" t="s" s="2">
-        <v>499</v>
+        <v>493</v>
       </c>
       <c r="P98" t="s" s="2">
         <v>71</v>
@@ -12353,13 +12357,13 @@
         <v>71</v>
       </c>
       <c r="X98" t="s" s="2">
-        <v>230</v>
+        <v>71</v>
       </c>
       <c r="Y98" t="s" s="2">
-        <v>500</v>
+        <v>71</v>
       </c>
       <c r="Z98" t="s" s="2">
-        <v>501</v>
+        <v>71</v>
       </c>
       <c r="AA98" t="s" s="2">
         <v>71</v>
@@ -12377,13 +12381,13 @@
         <v>71</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>495</v>
+        <v>488</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AH98" t="s" s="2">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="AI98" t="s" s="2">
         <v>90</v>
@@ -12394,10 +12398,10 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>502</v>
+        <v>494</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>502</v>
+        <v>494</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -12420,20 +12424,16 @@
         <v>71</v>
       </c>
       <c r="K99" t="s" s="2">
-        <v>503</v>
+        <v>146</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>504</v>
+        <v>147</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>505</v>
-      </c>
-      <c r="N99" t="s" s="2">
-        <v>506</v>
-      </c>
-      <c r="O99" t="s" s="2">
-        <v>507</v>
-      </c>
+        <v>148</v>
+      </c>
+      <c r="N99" s="2"/>
+      <c r="O99" s="2"/>
       <c r="P99" t="s" s="2">
         <v>71</v>
       </c>
@@ -12481,7 +12481,7 @@
         <v>71</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>502</v>
+        <v>149</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>72</v>
@@ -12490,22 +12490,22 @@
         <v>78</v>
       </c>
       <c r="AI99" t="s" s="2">
-        <v>90</v>
+        <v>71</v>
       </c>
       <c r="AJ99" t="s" s="2">
-        <v>91</v>
+        <v>71</v>
       </c>
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>508</v>
+        <v>495</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>508</v>
+        <v>495</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
-        <v>71</v>
+        <v>122</v>
       </c>
       <c r="E100" s="2"/>
       <c r="F100" t="s" s="2">
@@ -12524,18 +12524,18 @@
         <v>71</v>
       </c>
       <c r="K100" t="s" s="2">
-        <v>399</v>
+        <v>123</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>509</v>
+        <v>124</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>401</v>
-      </c>
-      <c r="N100" s="2"/>
-      <c r="O100" t="s" s="2">
-        <v>510</v>
-      </c>
+        <v>152</v>
+      </c>
+      <c r="N100" t="s" s="2">
+        <v>126</v>
+      </c>
+      <c r="O100" s="2"/>
       <c r="P100" t="s" s="2">
         <v>71</v>
       </c>
@@ -12571,9 +12571,11 @@
         <v>71</v>
       </c>
       <c r="AB100" t="s" s="2">
-        <v>511</v>
-      </c>
-      <c r="AC100" s="2"/>
+        <v>127</v>
+      </c>
+      <c r="AC100" t="s" s="2">
+        <v>128</v>
+      </c>
       <c r="AD100" t="s" s="2">
         <v>71</v>
       </c>
@@ -12581,7 +12583,7 @@
         <v>129</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>508</v>
+        <v>153</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>72</v>
@@ -12593,21 +12595,19 @@
         <v>90</v>
       </c>
       <c r="AJ100" t="s" s="2">
-        <v>512</v>
+        <v>131</v>
       </c>
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>513</v>
+        <v>496</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>508</v>
-      </c>
-      <c r="C101" t="s" s="2">
-        <v>514</v>
-      </c>
+        <v>496</v>
+      </c>
+      <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
-        <v>71</v>
+        <v>497</v>
       </c>
       <c r="E101" s="2"/>
       <c r="F101" t="s" s="2">
@@ -12620,23 +12620,25 @@
         <v>71</v>
       </c>
       <c r="I101" t="s" s="2">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="J101" t="s" s="2">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="K101" t="s" s="2">
-        <v>515</v>
+        <v>123</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>509</v>
+        <v>498</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>401</v>
-      </c>
-      <c r="N101" s="2"/>
+        <v>499</v>
+      </c>
+      <c r="N101" t="s" s="2">
+        <v>126</v>
+      </c>
       <c r="O101" t="s" s="2">
-        <v>510</v>
+        <v>204</v>
       </c>
       <c r="P101" t="s" s="2">
         <v>71</v>
@@ -12685,7 +12687,7 @@
         <v>71</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>508</v>
+        <v>500</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>72</v>
@@ -12697,15 +12699,15 @@
         <v>90</v>
       </c>
       <c r="AJ101" t="s" s="2">
-        <v>71</v>
+        <v>131</v>
       </c>
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>516</v>
+        <v>501</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>517</v>
+        <v>501</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -12728,16 +12730,20 @@
         <v>71</v>
       </c>
       <c r="K102" t="s" s="2">
-        <v>146</v>
+        <v>225</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>147</v>
+        <v>502</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>148</v>
-      </c>
-      <c r="N102" s="2"/>
-      <c r="O102" s="2"/>
+        <v>503</v>
+      </c>
+      <c r="N102" t="s" s="2">
+        <v>504</v>
+      </c>
+      <c r="O102" t="s" s="2">
+        <v>505</v>
+      </c>
       <c r="P102" t="s" s="2">
         <v>71</v>
       </c>
@@ -12761,13 +12767,13 @@
         <v>71</v>
       </c>
       <c r="X102" t="s" s="2">
-        <v>71</v>
+        <v>230</v>
       </c>
       <c r="Y102" t="s" s="2">
-        <v>71</v>
+        <v>506</v>
       </c>
       <c r="Z102" t="s" s="2">
-        <v>71</v>
+        <v>507</v>
       </c>
       <c r="AA102" t="s" s="2">
         <v>71</v>
@@ -12785,7 +12791,7 @@
         <v>71</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>149</v>
+        <v>501</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>72</v>
@@ -12794,29 +12800,29 @@
         <v>78</v>
       </c>
       <c r="AI102" t="s" s="2">
-        <v>71</v>
+        <v>90</v>
       </c>
       <c r="AJ102" t="s" s="2">
-        <v>71</v>
+        <v>91</v>
       </c>
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>518</v>
+        <v>508</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>519</v>
+        <v>508</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
-        <v>122</v>
+        <v>71</v>
       </c>
       <c r="E103" s="2"/>
       <c r="F103" t="s" s="2">
         <v>72</v>
       </c>
       <c r="G103" t="s" s="2">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="H103" t="s" s="2">
         <v>71</v>
@@ -12828,18 +12834,20 @@
         <v>71</v>
       </c>
       <c r="K103" t="s" s="2">
-        <v>123</v>
+        <v>509</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>124</v>
+        <v>510</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>152</v>
+        <v>511</v>
       </c>
       <c r="N103" t="s" s="2">
-        <v>126</v>
-      </c>
-      <c r="O103" s="2"/>
+        <v>512</v>
+      </c>
+      <c r="O103" t="s" s="2">
+        <v>513</v>
+      </c>
       <c r="P103" t="s" s="2">
         <v>71</v>
       </c>
@@ -12875,52 +12883,50 @@
         <v>71</v>
       </c>
       <c r="AB103" t="s" s="2">
-        <v>127</v>
+        <v>71</v>
       </c>
       <c r="AC103" t="s" s="2">
-        <v>128</v>
+        <v>71</v>
       </c>
       <c r="AD103" t="s" s="2">
         <v>71</v>
       </c>
       <c r="AE103" t="s" s="2">
-        <v>129</v>
+        <v>71</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>153</v>
+        <v>508</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AH103" t="s" s="2">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="AI103" t="s" s="2">
         <v>90</v>
       </c>
       <c r="AJ103" t="s" s="2">
-        <v>131</v>
+        <v>91</v>
       </c>
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>520</v>
+        <v>514</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>519</v>
-      </c>
-      <c r="C104" t="s" s="2">
-        <v>409</v>
-      </c>
+        <v>514</v>
+      </c>
+      <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
-        <v>122</v>
+        <v>71</v>
       </c>
       <c r="E104" s="2"/>
       <c r="F104" t="s" s="2">
         <v>72</v>
       </c>
       <c r="G104" t="s" s="2">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="H104" t="s" s="2">
         <v>71</v>
@@ -12932,18 +12938,18 @@
         <v>71</v>
       </c>
       <c r="K104" t="s" s="2">
-        <v>410</v>
+        <v>399</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>411</v>
+        <v>515</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>136</v>
-      </c>
-      <c r="N104" t="s" s="2">
-        <v>126</v>
-      </c>
-      <c r="O104" s="2"/>
+        <v>401</v>
+      </c>
+      <c r="N104" s="2"/>
+      <c r="O104" t="s" s="2">
+        <v>516</v>
+      </c>
       <c r="P104" t="s" s="2">
         <v>71</v>
       </c>
@@ -12979,19 +12985,17 @@
         <v>71</v>
       </c>
       <c r="AB104" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="AC104" t="s" s="2">
-        <v>71</v>
-      </c>
+        <v>517</v>
+      </c>
+      <c r="AC104" s="2"/>
       <c r="AD104" t="s" s="2">
         <v>71</v>
       </c>
       <c r="AE104" t="s" s="2">
-        <v>71</v>
+        <v>129</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>153</v>
+        <v>514</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>72</v>
@@ -13003,18 +13007,18 @@
         <v>90</v>
       </c>
       <c r="AJ104" t="s" s="2">
-        <v>131</v>
+        <v>518</v>
       </c>
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>519</v>
+        <v>514</v>
       </c>
       <c r="C105" t="s" s="2">
-        <v>522</v>
+        <v>520</v>
       </c>
       <c r="D105" t="s" s="2">
         <v>71</v>
@@ -13024,7 +13028,7 @@
         <v>72</v>
       </c>
       <c r="G105" t="s" s="2">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="H105" t="s" s="2">
         <v>71</v>
@@ -13036,16 +13040,18 @@
         <v>71</v>
       </c>
       <c r="K105" t="s" s="2">
-        <v>523</v>
+        <v>521</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>524</v>
+        <v>515</v>
       </c>
       <c r="M105" t="s" s="2">
-        <v>525</v>
+        <v>401</v>
       </c>
       <c r="N105" s="2"/>
-      <c r="O105" s="2"/>
+      <c r="O105" t="s" s="2">
+        <v>516</v>
+      </c>
       <c r="P105" t="s" s="2">
         <v>71</v>
       </c>
@@ -13093,7 +13099,7 @@
         <v>71</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>153</v>
+        <v>514</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>72</v>
@@ -13105,15 +13111,15 @@
         <v>90</v>
       </c>
       <c r="AJ105" t="s" s="2">
-        <v>131</v>
+        <v>71</v>
       </c>
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>526</v>
+        <v>522</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>527</v>
+        <v>523</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -13210,10 +13216,10 @@
     </row>
     <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>528</v>
+        <v>524</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>529</v>
+        <v>525</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -13312,16 +13318,16 @@
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>530</v>
+        <v>526</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>529</v>
+        <v>525</v>
       </c>
       <c r="C108" t="s" s="2">
-        <v>531</v>
+        <v>409</v>
       </c>
       <c r="D108" t="s" s="2">
-        <v>71</v>
+        <v>122</v>
       </c>
       <c r="E108" s="2"/>
       <c r="F108" t="s" s="2">
@@ -13340,16 +13346,16 @@
         <v>71</v>
       </c>
       <c r="K108" t="s" s="2">
-        <v>123</v>
+        <v>410</v>
       </c>
       <c r="L108" t="s" s="2">
-        <v>532</v>
+        <v>411</v>
       </c>
       <c r="M108" t="s" s="2">
-        <v>533</v>
+        <v>136</v>
       </c>
       <c r="N108" t="s" s="2">
-        <v>534</v>
+        <v>126</v>
       </c>
       <c r="O108" s="2"/>
       <c r="P108" t="s" s="2">
@@ -13416,12 +13422,14 @@
     </row>
     <row r="109" hidden="true">
       <c r="A109" t="s" s="2">
-        <v>535</v>
+        <v>527</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>536</v>
-      </c>
-      <c r="C109" s="2"/>
+        <v>525</v>
+      </c>
+      <c r="C109" t="s" s="2">
+        <v>528</v>
+      </c>
       <c r="D109" t="s" s="2">
         <v>71</v>
       </c>
@@ -13442,13 +13450,13 @@
         <v>71</v>
       </c>
       <c r="K109" t="s" s="2">
-        <v>146</v>
+        <v>529</v>
       </c>
       <c r="L109" t="s" s="2">
-        <v>147</v>
+        <v>530</v>
       </c>
       <c r="M109" t="s" s="2">
-        <v>148</v>
+        <v>531</v>
       </c>
       <c r="N109" s="2"/>
       <c r="O109" s="2"/>
@@ -13499,27 +13507,27 @@
         <v>71</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AH109" t="s" s="2">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="AI109" t="s" s="2">
-        <v>71</v>
+        <v>90</v>
       </c>
       <c r="AJ109" t="s" s="2">
-        <v>71</v>
+        <v>131</v>
       </c>
     </row>
     <row r="110" hidden="true">
       <c r="A110" t="s" s="2">
-        <v>537</v>
+        <v>532</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>538</v>
+        <v>533</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -13530,7 +13538,7 @@
         <v>72</v>
       </c>
       <c r="G110" t="s" s="2">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="H110" t="s" s="2">
         <v>71</v>
@@ -13542,13 +13550,13 @@
         <v>71</v>
       </c>
       <c r="K110" t="s" s="2">
-        <v>123</v>
+        <v>146</v>
       </c>
       <c r="L110" t="s" s="2">
-        <v>539</v>
+        <v>147</v>
       </c>
       <c r="M110" t="s" s="2">
-        <v>533</v>
+        <v>148</v>
       </c>
       <c r="N110" s="2"/>
       <c r="O110" s="2"/>
@@ -13587,50 +13595,50 @@
         <v>71</v>
       </c>
       <c r="AB110" t="s" s="2">
-        <v>127</v>
+        <v>71</v>
       </c>
       <c r="AC110" t="s" s="2">
-        <v>128</v>
+        <v>71</v>
       </c>
       <c r="AD110" t="s" s="2">
         <v>71</v>
       </c>
       <c r="AE110" t="s" s="2">
-        <v>129</v>
+        <v>71</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AH110" t="s" s="2">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="AI110" t="s" s="2">
-        <v>90</v>
+        <v>71</v>
       </c>
       <c r="AJ110" t="s" s="2">
-        <v>131</v>
+        <v>71</v>
       </c>
     </row>
     <row r="111" hidden="true">
       <c r="A111" t="s" s="2">
-        <v>540</v>
+        <v>534</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>541</v>
+        <v>535</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
-        <v>71</v>
+        <v>122</v>
       </c>
       <c r="E111" s="2"/>
       <c r="F111" t="s" s="2">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="G111" t="s" s="2">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="H111" t="s" s="2">
         <v>71</v>
@@ -13642,16 +13650,16 @@
         <v>71</v>
       </c>
       <c r="K111" t="s" s="2">
-        <v>93</v>
+        <v>123</v>
       </c>
       <c r="L111" t="s" s="2">
-        <v>156</v>
+        <v>124</v>
       </c>
       <c r="M111" t="s" s="2">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="N111" t="s" s="2">
-        <v>158</v>
+        <v>126</v>
       </c>
       <c r="O111" s="2"/>
       <c r="P111" t="s" s="2">
@@ -13659,7 +13667,7 @@
       </c>
       <c r="Q111" s="2"/>
       <c r="R111" t="s" s="2">
-        <v>531</v>
+        <v>71</v>
       </c>
       <c r="S111" t="s" s="2">
         <v>71</v>
@@ -13689,41 +13697,43 @@
         <v>71</v>
       </c>
       <c r="AB111" t="s" s="2">
-        <v>71</v>
+        <v>127</v>
       </c>
       <c r="AC111" t="s" s="2">
-        <v>71</v>
+        <v>128</v>
       </c>
       <c r="AD111" t="s" s="2">
         <v>71</v>
       </c>
       <c r="AE111" t="s" s="2">
-        <v>71</v>
+        <v>129</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>160</v>
+        <v>153</v>
       </c>
       <c r="AG111" t="s" s="2">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="AH111" t="s" s="2">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="AI111" t="s" s="2">
-        <v>71</v>
+        <v>90</v>
       </c>
       <c r="AJ111" t="s" s="2">
-        <v>71</v>
+        <v>131</v>
       </c>
     </row>
     <row r="112" hidden="true">
       <c r="A112" t="s" s="2">
-        <v>542</v>
+        <v>536</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>543</v>
-      </c>
-      <c r="C112" s="2"/>
+        <v>535</v>
+      </c>
+      <c r="C112" t="s" s="2">
+        <v>537</v>
+      </c>
       <c r="D112" t="s" s="2">
         <v>71</v>
       </c>
@@ -13744,15 +13754,17 @@
         <v>71</v>
       </c>
       <c r="K112" t="s" s="2">
-        <v>225</v>
+        <v>123</v>
       </c>
       <c r="L112" t="s" s="2">
-        <v>164</v>
+        <v>538</v>
       </c>
       <c r="M112" t="s" s="2">
-        <v>165</v>
-      </c>
-      <c r="N112" s="2"/>
+        <v>539</v>
+      </c>
+      <c r="N112" t="s" s="2">
+        <v>540</v>
+      </c>
       <c r="O112" s="2"/>
       <c r="P112" t="s" s="2">
         <v>71</v>
@@ -13789,41 +13801,41 @@
         <v>71</v>
       </c>
       <c r="AB112" t="s" s="2">
-        <v>166</v>
-      </c>
-      <c r="AC112" s="2"/>
+        <v>71</v>
+      </c>
+      <c r="AC112" t="s" s="2">
+        <v>71</v>
+      </c>
       <c r="AD112" t="s" s="2">
         <v>71</v>
       </c>
       <c r="AE112" t="s" s="2">
-        <v>167</v>
+        <v>71</v>
       </c>
       <c r="AF112" t="s" s="2">
-        <v>168</v>
+        <v>153</v>
       </c>
       <c r="AG112" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AH112" t="s" s="2">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="AI112" t="s" s="2">
         <v>90</v>
       </c>
       <c r="AJ112" t="s" s="2">
-        <v>91</v>
+        <v>131</v>
       </c>
     </row>
     <row r="113" hidden="true">
       <c r="A113" t="s" s="2">
-        <v>544</v>
+        <v>541</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>543</v>
-      </c>
-      <c r="C113" t="s" s="2">
-        <v>545</v>
-      </c>
+        <v>542</v>
+      </c>
+      <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
         <v>71</v>
       </c>
@@ -13844,13 +13856,13 @@
         <v>71</v>
       </c>
       <c r="K113" t="s" s="2">
-        <v>225</v>
+        <v>146</v>
       </c>
       <c r="L113" t="s" s="2">
-        <v>164</v>
+        <v>147</v>
       </c>
       <c r="M113" t="s" s="2">
-        <v>165</v>
+        <v>148</v>
       </c>
       <c r="N113" s="2"/>
       <c r="O113" s="2"/>
@@ -13877,13 +13889,13 @@
         <v>71</v>
       </c>
       <c r="X113" t="s" s="2">
-        <v>220</v>
+        <v>71</v>
       </c>
       <c r="Y113" t="s" s="2">
-        <v>546</v>
+        <v>71</v>
       </c>
       <c r="Z113" t="s" s="2">
-        <v>547</v>
+        <v>71</v>
       </c>
       <c r="AA113" t="s" s="2">
         <v>71</v>
@@ -13901,7 +13913,7 @@
         <v>71</v>
       </c>
       <c r="AF113" t="s" s="2">
-        <v>168</v>
+        <v>149</v>
       </c>
       <c r="AG113" t="s" s="2">
         <v>72</v>
@@ -13910,22 +13922,20 @@
         <v>78</v>
       </c>
       <c r="AI113" t="s" s="2">
-        <v>90</v>
+        <v>71</v>
       </c>
       <c r="AJ113" t="s" s="2">
-        <v>91</v>
+        <v>71</v>
       </c>
     </row>
     <row r="114" hidden="true">
       <c r="A114" t="s" s="2">
-        <v>548</v>
+        <v>543</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>529</v>
-      </c>
-      <c r="C114" t="s" s="2">
-        <v>138</v>
-      </c>
+        <v>544</v>
+      </c>
+      <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
         <v>71</v>
       </c>
@@ -13934,7 +13944,7 @@
         <v>72</v>
       </c>
       <c r="G114" t="s" s="2">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="H114" t="s" s="2">
         <v>71</v>
@@ -13949,14 +13959,12 @@
         <v>123</v>
       </c>
       <c r="L114" t="s" s="2">
-        <v>549</v>
+        <v>545</v>
       </c>
       <c r="M114" t="s" s="2">
-        <v>533</v>
-      </c>
-      <c r="N114" t="s" s="2">
-        <v>550</v>
-      </c>
+        <v>539</v>
+      </c>
+      <c r="N114" s="2"/>
       <c r="O114" s="2"/>
       <c r="P114" t="s" s="2">
         <v>71</v>
@@ -13993,16 +14001,16 @@
         <v>71</v>
       </c>
       <c r="AB114" t="s" s="2">
-        <v>71</v>
+        <v>127</v>
       </c>
       <c r="AC114" t="s" s="2">
-        <v>71</v>
+        <v>128</v>
       </c>
       <c r="AD114" t="s" s="2">
         <v>71</v>
       </c>
       <c r="AE114" t="s" s="2">
-        <v>71</v>
+        <v>129</v>
       </c>
       <c r="AF114" t="s" s="2">
         <v>153</v>
@@ -14022,10 +14030,10 @@
     </row>
     <row r="115" hidden="true">
       <c r="A115" t="s" s="2">
-        <v>551</v>
+        <v>546</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>536</v>
+        <v>547</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
@@ -14033,7 +14041,7 @@
       </c>
       <c r="E115" s="2"/>
       <c r="F115" t="s" s="2">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="G115" t="s" s="2">
         <v>78</v>
@@ -14048,22 +14056,24 @@
         <v>71</v>
       </c>
       <c r="K115" t="s" s="2">
-        <v>146</v>
+        <v>93</v>
       </c>
       <c r="L115" t="s" s="2">
-        <v>147</v>
+        <v>156</v>
       </c>
       <c r="M115" t="s" s="2">
-        <v>148</v>
-      </c>
-      <c r="N115" s="2"/>
+        <v>157</v>
+      </c>
+      <c r="N115" t="s" s="2">
+        <v>158</v>
+      </c>
       <c r="O115" s="2"/>
       <c r="P115" t="s" s="2">
         <v>71</v>
       </c>
       <c r="Q115" s="2"/>
       <c r="R115" t="s" s="2">
-        <v>71</v>
+        <v>537</v>
       </c>
       <c r="S115" t="s" s="2">
         <v>71</v>
@@ -14105,10 +14115,10 @@
         <v>71</v>
       </c>
       <c r="AF115" t="s" s="2">
-        <v>149</v>
+        <v>160</v>
       </c>
       <c r="AG115" t="s" s="2">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="AH115" t="s" s="2">
         <v>78</v>
@@ -14122,10 +14132,10 @@
     </row>
     <row r="116" hidden="true">
       <c r="A116" t="s" s="2">
-        <v>552</v>
+        <v>548</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>538</v>
+        <v>549</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
@@ -14136,7 +14146,7 @@
         <v>72</v>
       </c>
       <c r="G116" t="s" s="2">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="H116" t="s" s="2">
         <v>71</v>
@@ -14148,13 +14158,13 @@
         <v>71</v>
       </c>
       <c r="K116" t="s" s="2">
-        <v>123</v>
+        <v>225</v>
       </c>
       <c r="L116" t="s" s="2">
-        <v>539</v>
+        <v>164</v>
       </c>
       <c r="M116" t="s" s="2">
-        <v>533</v>
+        <v>165</v>
       </c>
       <c r="N116" s="2"/>
       <c r="O116" s="2"/>
@@ -14193,47 +14203,47 @@
         <v>71</v>
       </c>
       <c r="AB116" t="s" s="2">
-        <v>127</v>
-      </c>
-      <c r="AC116" t="s" s="2">
-        <v>128</v>
-      </c>
+        <v>166</v>
+      </c>
+      <c r="AC116" s="2"/>
       <c r="AD116" t="s" s="2">
         <v>71</v>
       </c>
       <c r="AE116" t="s" s="2">
-        <v>129</v>
+        <v>167</v>
       </c>
       <c r="AF116" t="s" s="2">
-        <v>153</v>
+        <v>168</v>
       </c>
       <c r="AG116" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AH116" t="s" s="2">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="AI116" t="s" s="2">
         <v>90</v>
       </c>
       <c r="AJ116" t="s" s="2">
-        <v>131</v>
+        <v>91</v>
       </c>
     </row>
     <row r="117" hidden="true">
       <c r="A117" t="s" s="2">
-        <v>553</v>
+        <v>550</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>541</v>
-      </c>
-      <c r="C117" s="2"/>
+        <v>549</v>
+      </c>
+      <c r="C117" t="s" s="2">
+        <v>551</v>
+      </c>
       <c r="D117" t="s" s="2">
         <v>71</v>
       </c>
       <c r="E117" s="2"/>
       <c r="F117" t="s" s="2">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="G117" t="s" s="2">
         <v>78</v>
@@ -14248,24 +14258,22 @@
         <v>71</v>
       </c>
       <c r="K117" t="s" s="2">
-        <v>93</v>
+        <v>225</v>
       </c>
       <c r="L117" t="s" s="2">
-        <v>156</v>
+        <v>164</v>
       </c>
       <c r="M117" t="s" s="2">
-        <v>157</v>
-      </c>
-      <c r="N117" t="s" s="2">
-        <v>158</v>
-      </c>
+        <v>165</v>
+      </c>
+      <c r="N117" s="2"/>
       <c r="O117" s="2"/>
       <c r="P117" t="s" s="2">
         <v>71</v>
       </c>
       <c r="Q117" s="2"/>
       <c r="R117" t="s" s="2">
-        <v>138</v>
+        <v>71</v>
       </c>
       <c r="S117" t="s" s="2">
         <v>71</v>
@@ -14283,13 +14291,13 @@
         <v>71</v>
       </c>
       <c r="X117" t="s" s="2">
-        <v>71</v>
+        <v>220</v>
       </c>
       <c r="Y117" t="s" s="2">
-        <v>71</v>
+        <v>552</v>
       </c>
       <c r="Z117" t="s" s="2">
-        <v>71</v>
+        <v>553</v>
       </c>
       <c r="AA117" t="s" s="2">
         <v>71</v>
@@ -14307,19 +14315,19 @@
         <v>71</v>
       </c>
       <c r="AF117" t="s" s="2">
-        <v>160</v>
+        <v>168</v>
       </c>
       <c r="AG117" t="s" s="2">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="AH117" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AI117" t="s" s="2">
-        <v>71</v>
+        <v>90</v>
       </c>
       <c r="AJ117" t="s" s="2">
-        <v>71</v>
+        <v>91</v>
       </c>
     </row>
     <row r="118" hidden="true">
@@ -14327,9 +14335,11 @@
         <v>554</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>543</v>
-      </c>
-      <c r="C118" s="2"/>
+        <v>535</v>
+      </c>
+      <c r="C118" t="s" s="2">
+        <v>138</v>
+      </c>
       <c r="D118" t="s" s="2">
         <v>71</v>
       </c>
@@ -14350,15 +14360,17 @@
         <v>71</v>
       </c>
       <c r="K118" t="s" s="2">
-        <v>146</v>
+        <v>123</v>
       </c>
       <c r="L118" t="s" s="2">
-        <v>164</v>
+        <v>555</v>
       </c>
       <c r="M118" t="s" s="2">
-        <v>165</v>
-      </c>
-      <c r="N118" s="2"/>
+        <v>539</v>
+      </c>
+      <c r="N118" t="s" s="2">
+        <v>556</v>
+      </c>
       <c r="O118" s="2"/>
       <c r="P118" t="s" s="2">
         <v>71</v>
@@ -14407,31 +14419,29 @@
         <v>71</v>
       </c>
       <c r="AF118" t="s" s="2">
-        <v>168</v>
+        <v>153</v>
       </c>
       <c r="AG118" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AH118" t="s" s="2">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="AI118" t="s" s="2">
         <v>90</v>
       </c>
       <c r="AJ118" t="s" s="2">
-        <v>91</v>
+        <v>131</v>
       </c>
     </row>
     <row r="119" hidden="true">
       <c r="A119" t="s" s="2">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>529</v>
-      </c>
-      <c r="C119" t="s" s="2">
-        <v>556</v>
-      </c>
+        <v>542</v>
+      </c>
+      <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
         <v>71</v>
       </c>
@@ -14452,17 +14462,15 @@
         <v>71</v>
       </c>
       <c r="K119" t="s" s="2">
-        <v>123</v>
+        <v>146</v>
       </c>
       <c r="L119" t="s" s="2">
-        <v>557</v>
+        <v>147</v>
       </c>
       <c r="M119" t="s" s="2">
-        <v>533</v>
-      </c>
-      <c r="N119" t="s" s="2">
-        <v>558</v>
-      </c>
+        <v>148</v>
+      </c>
+      <c r="N119" s="2"/>
       <c r="O119" s="2"/>
       <c r="P119" t="s" s="2">
         <v>71</v>
@@ -14511,27 +14519,27 @@
         <v>71</v>
       </c>
       <c r="AF119" t="s" s="2">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="AG119" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AH119" t="s" s="2">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="AI119" t="s" s="2">
-        <v>90</v>
+        <v>71</v>
       </c>
       <c r="AJ119" t="s" s="2">
-        <v>131</v>
+        <v>71</v>
       </c>
     </row>
     <row r="120" hidden="true">
       <c r="A120" t="s" s="2">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>536</v>
+        <v>544</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
@@ -14542,7 +14550,7 @@
         <v>72</v>
       </c>
       <c r="G120" t="s" s="2">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="H120" t="s" s="2">
         <v>71</v>
@@ -14554,13 +14562,13 @@
         <v>71</v>
       </c>
       <c r="K120" t="s" s="2">
-        <v>146</v>
+        <v>123</v>
       </c>
       <c r="L120" t="s" s="2">
-        <v>147</v>
+        <v>545</v>
       </c>
       <c r="M120" t="s" s="2">
-        <v>148</v>
+        <v>539</v>
       </c>
       <c r="N120" s="2"/>
       <c r="O120" s="2"/>
@@ -14599,39 +14607,39 @@
         <v>71</v>
       </c>
       <c r="AB120" t="s" s="2">
-        <v>71</v>
+        <v>127</v>
       </c>
       <c r="AC120" t="s" s="2">
-        <v>71</v>
+        <v>128</v>
       </c>
       <c r="AD120" t="s" s="2">
         <v>71</v>
       </c>
       <c r="AE120" t="s" s="2">
-        <v>71</v>
+        <v>129</v>
       </c>
       <c r="AF120" t="s" s="2">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="AG120" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AH120" t="s" s="2">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="AI120" t="s" s="2">
-        <v>71</v>
+        <v>90</v>
       </c>
       <c r="AJ120" t="s" s="2">
-        <v>71</v>
+        <v>131</v>
       </c>
     </row>
     <row r="121" hidden="true">
       <c r="A121" t="s" s="2">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>538</v>
+        <v>547</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
@@ -14639,10 +14647,10 @@
       </c>
       <c r="E121" s="2"/>
       <c r="F121" t="s" s="2">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="G121" t="s" s="2">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="H121" t="s" s="2">
         <v>71</v>
@@ -14654,22 +14662,24 @@
         <v>71</v>
       </c>
       <c r="K121" t="s" s="2">
-        <v>123</v>
+        <v>93</v>
       </c>
       <c r="L121" t="s" s="2">
-        <v>539</v>
+        <v>156</v>
       </c>
       <c r="M121" t="s" s="2">
-        <v>533</v>
-      </c>
-      <c r="N121" s="2"/>
+        <v>157</v>
+      </c>
+      <c r="N121" t="s" s="2">
+        <v>158</v>
+      </c>
       <c r="O121" s="2"/>
       <c r="P121" t="s" s="2">
         <v>71</v>
       </c>
       <c r="Q121" s="2"/>
       <c r="R121" t="s" s="2">
-        <v>71</v>
+        <v>138</v>
       </c>
       <c r="S121" t="s" s="2">
         <v>71</v>
@@ -14699,39 +14709,39 @@
         <v>71</v>
       </c>
       <c r="AB121" t="s" s="2">
-        <v>127</v>
+        <v>71</v>
       </c>
       <c r="AC121" t="s" s="2">
-        <v>128</v>
+        <v>71</v>
       </c>
       <c r="AD121" t="s" s="2">
         <v>71</v>
       </c>
       <c r="AE121" t="s" s="2">
-        <v>129</v>
+        <v>71</v>
       </c>
       <c r="AF121" t="s" s="2">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="AG121" t="s" s="2">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="AH121" t="s" s="2">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="AI121" t="s" s="2">
-        <v>90</v>
+        <v>71</v>
       </c>
       <c r="AJ121" t="s" s="2">
-        <v>131</v>
+        <v>71</v>
       </c>
     </row>
     <row r="122" hidden="true">
       <c r="A122" t="s" s="2">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>541</v>
+        <v>549</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
@@ -14739,7 +14749,7 @@
       </c>
       <c r="E122" s="2"/>
       <c r="F122" t="s" s="2">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="G122" t="s" s="2">
         <v>78</v>
@@ -14754,24 +14764,22 @@
         <v>71</v>
       </c>
       <c r="K122" t="s" s="2">
-        <v>93</v>
+        <v>146</v>
       </c>
       <c r="L122" t="s" s="2">
-        <v>156</v>
+        <v>164</v>
       </c>
       <c r="M122" t="s" s="2">
-        <v>157</v>
-      </c>
-      <c r="N122" t="s" s="2">
-        <v>158</v>
-      </c>
+        <v>165</v>
+      </c>
+      <c r="N122" s="2"/>
       <c r="O122" s="2"/>
       <c r="P122" t="s" s="2">
         <v>71</v>
       </c>
       <c r="Q122" s="2"/>
       <c r="R122" t="s" s="2">
-        <v>556</v>
+        <v>71</v>
       </c>
       <c r="S122" t="s" s="2">
         <v>71</v>
@@ -14813,29 +14821,31 @@
         <v>71</v>
       </c>
       <c r="AF122" t="s" s="2">
-        <v>160</v>
+        <v>168</v>
       </c>
       <c r="AG122" t="s" s="2">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="AH122" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AI122" t="s" s="2">
-        <v>71</v>
+        <v>90</v>
       </c>
       <c r="AJ122" t="s" s="2">
-        <v>71</v>
+        <v>91</v>
       </c>
     </row>
     <row r="123" hidden="true">
       <c r="A123" t="s" s="2">
+        <v>561</v>
+      </c>
+      <c r="B123" t="s" s="2">
+        <v>535</v>
+      </c>
+      <c r="C123" t="s" s="2">
         <v>562</v>
       </c>
-      <c r="B123" t="s" s="2">
-        <v>543</v>
-      </c>
-      <c r="C123" s="2"/>
       <c r="D123" t="s" s="2">
         <v>71</v>
       </c>
@@ -14844,7 +14854,7 @@
         <v>72</v>
       </c>
       <c r="G123" t="s" s="2">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="H123" t="s" s="2">
         <v>71</v>
@@ -14856,13 +14866,13 @@
         <v>71</v>
       </c>
       <c r="K123" t="s" s="2">
-        <v>146</v>
+        <v>123</v>
       </c>
       <c r="L123" t="s" s="2">
-        <v>164</v>
+        <v>545</v>
       </c>
       <c r="M123" t="s" s="2">
-        <v>165</v>
+        <v>539</v>
       </c>
       <c r="N123" s="2"/>
       <c r="O123" s="2"/>
@@ -14913,19 +14923,19 @@
         <v>71</v>
       </c>
       <c r="AF123" t="s" s="2">
-        <v>168</v>
+        <v>153</v>
       </c>
       <c r="AG123" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AH123" t="s" s="2">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="AI123" t="s" s="2">
         <v>90</v>
       </c>
       <c r="AJ123" t="s" s="2">
-        <v>91</v>
+        <v>131</v>
       </c>
     </row>
     <row r="124" hidden="true">
@@ -14933,11 +14943,9 @@
         <v>563</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>529</v>
-      </c>
-      <c r="C124" t="s" s="2">
-        <v>564</v>
-      </c>
+        <v>542</v>
+      </c>
+      <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
         <v>71</v>
       </c>
@@ -14958,17 +14966,15 @@
         <v>71</v>
       </c>
       <c r="K124" t="s" s="2">
-        <v>123</v>
+        <v>146</v>
       </c>
       <c r="L124" t="s" s="2">
-        <v>565</v>
+        <v>147</v>
       </c>
       <c r="M124" t="s" s="2">
-        <v>533</v>
-      </c>
-      <c r="N124" t="s" s="2">
-        <v>566</v>
-      </c>
+        <v>148</v>
+      </c>
+      <c r="N124" s="2"/>
       <c r="O124" s="2"/>
       <c r="P124" t="s" s="2">
         <v>71</v>
@@ -15017,27 +15023,27 @@
         <v>71</v>
       </c>
       <c r="AF124" t="s" s="2">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="AG124" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AH124" t="s" s="2">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="AI124" t="s" s="2">
-        <v>90</v>
+        <v>71</v>
       </c>
       <c r="AJ124" t="s" s="2">
-        <v>131</v>
+        <v>71</v>
       </c>
     </row>
     <row r="125" hidden="true">
       <c r="A125" t="s" s="2">
-        <v>567</v>
+        <v>564</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>536</v>
+        <v>544</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
@@ -15048,7 +15054,7 @@
         <v>72</v>
       </c>
       <c r="G125" t="s" s="2">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="H125" t="s" s="2">
         <v>71</v>
@@ -15060,13 +15066,13 @@
         <v>71</v>
       </c>
       <c r="K125" t="s" s="2">
-        <v>146</v>
+        <v>123</v>
       </c>
       <c r="L125" t="s" s="2">
-        <v>147</v>
+        <v>545</v>
       </c>
       <c r="M125" t="s" s="2">
-        <v>148</v>
+        <v>539</v>
       </c>
       <c r="N125" s="2"/>
       <c r="O125" s="2"/>
@@ -15105,39 +15111,39 @@
         <v>71</v>
       </c>
       <c r="AB125" t="s" s="2">
-        <v>71</v>
+        <v>127</v>
       </c>
       <c r="AC125" t="s" s="2">
-        <v>71</v>
+        <v>128</v>
       </c>
       <c r="AD125" t="s" s="2">
         <v>71</v>
       </c>
       <c r="AE125" t="s" s="2">
-        <v>71</v>
+        <v>129</v>
       </c>
       <c r="AF125" t="s" s="2">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="AG125" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AH125" t="s" s="2">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="AI125" t="s" s="2">
-        <v>71</v>
+        <v>90</v>
       </c>
       <c r="AJ125" t="s" s="2">
-        <v>71</v>
+        <v>131</v>
       </c>
     </row>
     <row r="126" hidden="true">
       <c r="A126" t="s" s="2">
-        <v>568</v>
+        <v>565</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>538</v>
+        <v>547</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" t="s" s="2">
@@ -15145,10 +15151,10 @@
       </c>
       <c r="E126" s="2"/>
       <c r="F126" t="s" s="2">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="G126" t="s" s="2">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="H126" t="s" s="2">
         <v>71</v>
@@ -15160,22 +15166,24 @@
         <v>71</v>
       </c>
       <c r="K126" t="s" s="2">
-        <v>123</v>
+        <v>93</v>
       </c>
       <c r="L126" t="s" s="2">
-        <v>539</v>
+        <v>156</v>
       </c>
       <c r="M126" t="s" s="2">
-        <v>533</v>
-      </c>
-      <c r="N126" s="2"/>
+        <v>157</v>
+      </c>
+      <c r="N126" t="s" s="2">
+        <v>158</v>
+      </c>
       <c r="O126" s="2"/>
       <c r="P126" t="s" s="2">
         <v>71</v>
       </c>
       <c r="Q126" s="2"/>
       <c r="R126" t="s" s="2">
-        <v>71</v>
+        <v>562</v>
       </c>
       <c r="S126" t="s" s="2">
         <v>71</v>
@@ -15205,39 +15213,39 @@
         <v>71</v>
       </c>
       <c r="AB126" t="s" s="2">
-        <v>127</v>
+        <v>71</v>
       </c>
       <c r="AC126" t="s" s="2">
-        <v>128</v>
+        <v>71</v>
       </c>
       <c r="AD126" t="s" s="2">
         <v>71</v>
       </c>
       <c r="AE126" t="s" s="2">
-        <v>129</v>
+        <v>71</v>
       </c>
       <c r="AF126" t="s" s="2">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="AG126" t="s" s="2">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="AH126" t="s" s="2">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="AI126" t="s" s="2">
-        <v>90</v>
+        <v>71</v>
       </c>
       <c r="AJ126" t="s" s="2">
-        <v>131</v>
+        <v>71</v>
       </c>
     </row>
     <row r="127" hidden="true">
       <c r="A127" t="s" s="2">
-        <v>569</v>
+        <v>566</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>541</v>
+        <v>549</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
@@ -15245,7 +15253,7 @@
       </c>
       <c r="E127" s="2"/>
       <c r="F127" t="s" s="2">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="G127" t="s" s="2">
         <v>78</v>
@@ -15260,24 +15268,22 @@
         <v>71</v>
       </c>
       <c r="K127" t="s" s="2">
-        <v>93</v>
+        <v>146</v>
       </c>
       <c r="L127" t="s" s="2">
-        <v>156</v>
+        <v>164</v>
       </c>
       <c r="M127" t="s" s="2">
-        <v>157</v>
-      </c>
-      <c r="N127" t="s" s="2">
-        <v>158</v>
-      </c>
+        <v>165</v>
+      </c>
+      <c r="N127" s="2"/>
       <c r="O127" s="2"/>
       <c r="P127" t="s" s="2">
         <v>71</v>
       </c>
       <c r="Q127" s="2"/>
       <c r="R127" t="s" s="2">
-        <v>564</v>
+        <v>71</v>
       </c>
       <c r="S127" t="s" s="2">
         <v>71</v>
@@ -15319,29 +15325,31 @@
         <v>71</v>
       </c>
       <c r="AF127" t="s" s="2">
-        <v>160</v>
+        <v>168</v>
       </c>
       <c r="AG127" t="s" s="2">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="AH127" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AI127" t="s" s="2">
-        <v>71</v>
+        <v>90</v>
       </c>
       <c r="AJ127" t="s" s="2">
-        <v>71</v>
+        <v>91</v>
       </c>
     </row>
     <row r="128" hidden="true">
       <c r="A128" t="s" s="2">
-        <v>570</v>
+        <v>567</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>543</v>
-      </c>
-      <c r="C128" s="2"/>
+        <v>535</v>
+      </c>
+      <c r="C128" t="s" s="2">
+        <v>568</v>
+      </c>
       <c r="D128" t="s" s="2">
         <v>71</v>
       </c>
@@ -15362,15 +15370,17 @@
         <v>71</v>
       </c>
       <c r="K128" t="s" s="2">
-        <v>146</v>
+        <v>123</v>
       </c>
       <c r="L128" t="s" s="2">
-        <v>164</v>
+        <v>569</v>
       </c>
       <c r="M128" t="s" s="2">
-        <v>165</v>
-      </c>
-      <c r="N128" s="2"/>
+        <v>539</v>
+      </c>
+      <c r="N128" t="s" s="2">
+        <v>570</v>
+      </c>
       <c r="O128" s="2"/>
       <c r="P128" t="s" s="2">
         <v>71</v>
@@ -15419,19 +15429,19 @@
         <v>71</v>
       </c>
       <c r="AF128" t="s" s="2">
-        <v>168</v>
+        <v>153</v>
       </c>
       <c r="AG128" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AH128" t="s" s="2">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="AI128" t="s" s="2">
         <v>90</v>
       </c>
       <c r="AJ128" t="s" s="2">
-        <v>91</v>
+        <v>131</v>
       </c>
     </row>
     <row r="129" hidden="true">
@@ -15439,11 +15449,9 @@
         <v>571</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>529</v>
-      </c>
-      <c r="C129" t="s" s="2">
-        <v>572</v>
-      </c>
+        <v>542</v>
+      </c>
+      <c r="C129" s="2"/>
       <c r="D129" t="s" s="2">
         <v>71</v>
       </c>
@@ -15464,17 +15472,15 @@
         <v>71</v>
       </c>
       <c r="K129" t="s" s="2">
-        <v>123</v>
+        <v>146</v>
       </c>
       <c r="L129" t="s" s="2">
-        <v>573</v>
+        <v>147</v>
       </c>
       <c r="M129" t="s" s="2">
-        <v>533</v>
-      </c>
-      <c r="N129" t="s" s="2">
-        <v>574</v>
-      </c>
+        <v>148</v>
+      </c>
+      <c r="N129" s="2"/>
       <c r="O129" s="2"/>
       <c r="P129" t="s" s="2">
         <v>71</v>
@@ -15523,27 +15529,27 @@
         <v>71</v>
       </c>
       <c r="AF129" t="s" s="2">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="AG129" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AH129" t="s" s="2">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="AI129" t="s" s="2">
-        <v>90</v>
+        <v>71</v>
       </c>
       <c r="AJ129" t="s" s="2">
-        <v>131</v>
+        <v>71</v>
       </c>
     </row>
     <row r="130" hidden="true">
       <c r="A130" t="s" s="2">
-        <v>575</v>
+        <v>572</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>536</v>
+        <v>544</v>
       </c>
       <c r="C130" s="2"/>
       <c r="D130" t="s" s="2">
@@ -15554,7 +15560,7 @@
         <v>72</v>
       </c>
       <c r="G130" t="s" s="2">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="H130" t="s" s="2">
         <v>71</v>
@@ -15566,13 +15572,13 @@
         <v>71</v>
       </c>
       <c r="K130" t="s" s="2">
-        <v>146</v>
+        <v>123</v>
       </c>
       <c r="L130" t="s" s="2">
-        <v>147</v>
+        <v>545</v>
       </c>
       <c r="M130" t="s" s="2">
-        <v>148</v>
+        <v>539</v>
       </c>
       <c r="N130" s="2"/>
       <c r="O130" s="2"/>
@@ -15611,39 +15617,39 @@
         <v>71</v>
       </c>
       <c r="AB130" t="s" s="2">
-        <v>71</v>
+        <v>127</v>
       </c>
       <c r="AC130" t="s" s="2">
-        <v>71</v>
+        <v>128</v>
       </c>
       <c r="AD130" t="s" s="2">
         <v>71</v>
       </c>
       <c r="AE130" t="s" s="2">
-        <v>71</v>
+        <v>129</v>
       </c>
       <c r="AF130" t="s" s="2">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="AG130" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AH130" t="s" s="2">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="AI130" t="s" s="2">
-        <v>71</v>
+        <v>90</v>
       </c>
       <c r="AJ130" t="s" s="2">
-        <v>71</v>
+        <v>131</v>
       </c>
     </row>
     <row r="131" hidden="true">
       <c r="A131" t="s" s="2">
-        <v>576</v>
+        <v>573</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>538</v>
+        <v>547</v>
       </c>
       <c r="C131" s="2"/>
       <c r="D131" t="s" s="2">
@@ -15651,10 +15657,10 @@
       </c>
       <c r="E131" s="2"/>
       <c r="F131" t="s" s="2">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="G131" t="s" s="2">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="H131" t="s" s="2">
         <v>71</v>
@@ -15666,22 +15672,24 @@
         <v>71</v>
       </c>
       <c r="K131" t="s" s="2">
-        <v>123</v>
+        <v>93</v>
       </c>
       <c r="L131" t="s" s="2">
-        <v>539</v>
+        <v>156</v>
       </c>
       <c r="M131" t="s" s="2">
-        <v>533</v>
-      </c>
-      <c r="N131" s="2"/>
+        <v>157</v>
+      </c>
+      <c r="N131" t="s" s="2">
+        <v>158</v>
+      </c>
       <c r="O131" s="2"/>
       <c r="P131" t="s" s="2">
         <v>71</v>
       </c>
       <c r="Q131" s="2"/>
       <c r="R131" t="s" s="2">
-        <v>71</v>
+        <v>568</v>
       </c>
       <c r="S131" t="s" s="2">
         <v>71</v>
@@ -15711,39 +15719,39 @@
         <v>71</v>
       </c>
       <c r="AB131" t="s" s="2">
-        <v>127</v>
+        <v>71</v>
       </c>
       <c r="AC131" t="s" s="2">
-        <v>128</v>
+        <v>71</v>
       </c>
       <c r="AD131" t="s" s="2">
         <v>71</v>
       </c>
       <c r="AE131" t="s" s="2">
-        <v>129</v>
+        <v>71</v>
       </c>
       <c r="AF131" t="s" s="2">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="AG131" t="s" s="2">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="AH131" t="s" s="2">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="AI131" t="s" s="2">
-        <v>90</v>
+        <v>71</v>
       </c>
       <c r="AJ131" t="s" s="2">
-        <v>131</v>
+        <v>71</v>
       </c>
     </row>
     <row r="132" hidden="true">
       <c r="A132" t="s" s="2">
-        <v>577</v>
+        <v>574</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>541</v>
+        <v>549</v>
       </c>
       <c r="C132" s="2"/>
       <c r="D132" t="s" s="2">
@@ -15751,7 +15759,7 @@
       </c>
       <c r="E132" s="2"/>
       <c r="F132" t="s" s="2">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="G132" t="s" s="2">
         <v>78</v>
@@ -15766,24 +15774,22 @@
         <v>71</v>
       </c>
       <c r="K132" t="s" s="2">
-        <v>93</v>
+        <v>146</v>
       </c>
       <c r="L132" t="s" s="2">
-        <v>156</v>
+        <v>164</v>
       </c>
       <c r="M132" t="s" s="2">
-        <v>157</v>
-      </c>
-      <c r="N132" t="s" s="2">
-        <v>158</v>
-      </c>
+        <v>165</v>
+      </c>
+      <c r="N132" s="2"/>
       <c r="O132" s="2"/>
       <c r="P132" t="s" s="2">
         <v>71</v>
       </c>
       <c r="Q132" s="2"/>
       <c r="R132" t="s" s="2">
-        <v>572</v>
+        <v>71</v>
       </c>
       <c r="S132" t="s" s="2">
         <v>71</v>
@@ -15825,29 +15831,31 @@
         <v>71</v>
       </c>
       <c r="AF132" t="s" s="2">
-        <v>160</v>
+        <v>168</v>
       </c>
       <c r="AG132" t="s" s="2">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="AH132" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AI132" t="s" s="2">
-        <v>71</v>
+        <v>90</v>
       </c>
       <c r="AJ132" t="s" s="2">
-        <v>71</v>
+        <v>91</v>
       </c>
     </row>
     <row r="133" hidden="true">
       <c r="A133" t="s" s="2">
-        <v>578</v>
+        <v>575</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>543</v>
-      </c>
-      <c r="C133" s="2"/>
+        <v>535</v>
+      </c>
+      <c r="C133" t="s" s="2">
+        <v>576</v>
+      </c>
       <c r="D133" t="s" s="2">
         <v>71</v>
       </c>
@@ -15856,7 +15864,7 @@
         <v>72</v>
       </c>
       <c r="G133" t="s" s="2">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="H133" t="s" s="2">
         <v>71</v>
@@ -15868,13 +15876,13 @@
         <v>71</v>
       </c>
       <c r="K133" t="s" s="2">
-        <v>146</v>
+        <v>123</v>
       </c>
       <c r="L133" t="s" s="2">
-        <v>164</v>
+        <v>545</v>
       </c>
       <c r="M133" t="s" s="2">
-        <v>165</v>
+        <v>539</v>
       </c>
       <c r="N133" s="2"/>
       <c r="O133" s="2"/>
@@ -15925,31 +15933,29 @@
         <v>71</v>
       </c>
       <c r="AF133" t="s" s="2">
-        <v>168</v>
+        <v>153</v>
       </c>
       <c r="AG133" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AH133" t="s" s="2">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="AI133" t="s" s="2">
         <v>90</v>
       </c>
       <c r="AJ133" t="s" s="2">
-        <v>91</v>
+        <v>131</v>
       </c>
     </row>
     <row r="134" hidden="true">
       <c r="A134" t="s" s="2">
-        <v>579</v>
+        <v>577</v>
       </c>
       <c r="B134" t="s" s="2">
-        <v>529</v>
-      </c>
-      <c r="C134" t="s" s="2">
-        <v>580</v>
-      </c>
+        <v>542</v>
+      </c>
+      <c r="C134" s="2"/>
       <c r="D134" t="s" s="2">
         <v>71</v>
       </c>
@@ -15970,17 +15976,15 @@
         <v>71</v>
       </c>
       <c r="K134" t="s" s="2">
-        <v>123</v>
+        <v>146</v>
       </c>
       <c r="L134" t="s" s="2">
-        <v>581</v>
+        <v>147</v>
       </c>
       <c r="M134" t="s" s="2">
-        <v>533</v>
-      </c>
-      <c r="N134" t="s" s="2">
-        <v>582</v>
-      </c>
+        <v>148</v>
+      </c>
+      <c r="N134" s="2"/>
       <c r="O134" s="2"/>
       <c r="P134" t="s" s="2">
         <v>71</v>
@@ -16029,27 +16033,27 @@
         <v>71</v>
       </c>
       <c r="AF134" t="s" s="2">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="AG134" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AH134" t="s" s="2">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="AI134" t="s" s="2">
-        <v>90</v>
+        <v>71</v>
       </c>
       <c r="AJ134" t="s" s="2">
-        <v>131</v>
+        <v>71</v>
       </c>
     </row>
     <row r="135" hidden="true">
       <c r="A135" t="s" s="2">
-        <v>583</v>
+        <v>578</v>
       </c>
       <c r="B135" t="s" s="2">
-        <v>536</v>
+        <v>544</v>
       </c>
       <c r="C135" s="2"/>
       <c r="D135" t="s" s="2">
@@ -16060,7 +16064,7 @@
         <v>72</v>
       </c>
       <c r="G135" t="s" s="2">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="H135" t="s" s="2">
         <v>71</v>
@@ -16072,13 +16076,13 @@
         <v>71</v>
       </c>
       <c r="K135" t="s" s="2">
-        <v>146</v>
+        <v>123</v>
       </c>
       <c r="L135" t="s" s="2">
-        <v>147</v>
+        <v>545</v>
       </c>
       <c r="M135" t="s" s="2">
-        <v>148</v>
+        <v>539</v>
       </c>
       <c r="N135" s="2"/>
       <c r="O135" s="2"/>
@@ -16117,39 +16121,39 @@
         <v>71</v>
       </c>
       <c r="AB135" t="s" s="2">
-        <v>71</v>
+        <v>127</v>
       </c>
       <c r="AC135" t="s" s="2">
-        <v>71</v>
+        <v>128</v>
       </c>
       <c r="AD135" t="s" s="2">
         <v>71</v>
       </c>
       <c r="AE135" t="s" s="2">
-        <v>71</v>
+        <v>129</v>
       </c>
       <c r="AF135" t="s" s="2">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="AG135" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AH135" t="s" s="2">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="AI135" t="s" s="2">
-        <v>71</v>
+        <v>90</v>
       </c>
       <c r="AJ135" t="s" s="2">
-        <v>71</v>
+        <v>131</v>
       </c>
     </row>
     <row r="136" hidden="true">
       <c r="A136" t="s" s="2">
-        <v>584</v>
+        <v>579</v>
       </c>
       <c r="B136" t="s" s="2">
-        <v>538</v>
+        <v>547</v>
       </c>
       <c r="C136" s="2"/>
       <c r="D136" t="s" s="2">
@@ -16157,10 +16161,10 @@
       </c>
       <c r="E136" s="2"/>
       <c r="F136" t="s" s="2">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="G136" t="s" s="2">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="H136" t="s" s="2">
         <v>71</v>
@@ -16172,22 +16176,24 @@
         <v>71</v>
       </c>
       <c r="K136" t="s" s="2">
-        <v>123</v>
+        <v>93</v>
       </c>
       <c r="L136" t="s" s="2">
-        <v>539</v>
+        <v>156</v>
       </c>
       <c r="M136" t="s" s="2">
-        <v>533</v>
-      </c>
-      <c r="N136" s="2"/>
+        <v>157</v>
+      </c>
+      <c r="N136" t="s" s="2">
+        <v>158</v>
+      </c>
       <c r="O136" s="2"/>
       <c r="P136" t="s" s="2">
         <v>71</v>
       </c>
       <c r="Q136" s="2"/>
       <c r="R136" t="s" s="2">
-        <v>71</v>
+        <v>576</v>
       </c>
       <c r="S136" t="s" s="2">
         <v>71</v>
@@ -16217,39 +16223,39 @@
         <v>71</v>
       </c>
       <c r="AB136" t="s" s="2">
-        <v>127</v>
+        <v>71</v>
       </c>
       <c r="AC136" t="s" s="2">
-        <v>128</v>
+        <v>71</v>
       </c>
       <c r="AD136" t="s" s="2">
         <v>71</v>
       </c>
       <c r="AE136" t="s" s="2">
-        <v>129</v>
+        <v>71</v>
       </c>
       <c r="AF136" t="s" s="2">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="AG136" t="s" s="2">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="AH136" t="s" s="2">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="AI136" t="s" s="2">
-        <v>90</v>
+        <v>71</v>
       </c>
       <c r="AJ136" t="s" s="2">
-        <v>131</v>
+        <v>71</v>
       </c>
     </row>
     <row r="137" hidden="true">
       <c r="A137" t="s" s="2">
-        <v>585</v>
+        <v>580</v>
       </c>
       <c r="B137" t="s" s="2">
-        <v>541</v>
+        <v>549</v>
       </c>
       <c r="C137" s="2"/>
       <c r="D137" t="s" s="2">
@@ -16257,7 +16263,7 @@
       </c>
       <c r="E137" s="2"/>
       <c r="F137" t="s" s="2">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="G137" t="s" s="2">
         <v>78</v>
@@ -16272,24 +16278,22 @@
         <v>71</v>
       </c>
       <c r="K137" t="s" s="2">
-        <v>93</v>
+        <v>146</v>
       </c>
       <c r="L137" t="s" s="2">
-        <v>156</v>
+        <v>164</v>
       </c>
       <c r="M137" t="s" s="2">
-        <v>157</v>
-      </c>
-      <c r="N137" t="s" s="2">
-        <v>158</v>
-      </c>
+        <v>165</v>
+      </c>
+      <c r="N137" s="2"/>
       <c r="O137" s="2"/>
       <c r="P137" t="s" s="2">
         <v>71</v>
       </c>
       <c r="Q137" s="2"/>
       <c r="R137" t="s" s="2">
-        <v>580</v>
+        <v>71</v>
       </c>
       <c r="S137" t="s" s="2">
         <v>71</v>
@@ -16331,29 +16335,31 @@
         <v>71</v>
       </c>
       <c r="AF137" t="s" s="2">
-        <v>160</v>
+        <v>168</v>
       </c>
       <c r="AG137" t="s" s="2">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="AH137" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AI137" t="s" s="2">
-        <v>71</v>
+        <v>90</v>
       </c>
       <c r="AJ137" t="s" s="2">
-        <v>71</v>
+        <v>91</v>
       </c>
     </row>
     <row r="138" hidden="true">
       <c r="A138" t="s" s="2">
-        <v>586</v>
+        <v>581</v>
       </c>
       <c r="B138" t="s" s="2">
-        <v>543</v>
-      </c>
-      <c r="C138" s="2"/>
+        <v>535</v>
+      </c>
+      <c r="C138" t="s" s="2">
+        <v>582</v>
+      </c>
       <c r="D138" t="s" s="2">
         <v>71</v>
       </c>
@@ -16374,15 +16380,17 @@
         <v>71</v>
       </c>
       <c r="K138" t="s" s="2">
-        <v>262</v>
+        <v>123</v>
       </c>
       <c r="L138" t="s" s="2">
-        <v>164</v>
+        <v>583</v>
       </c>
       <c r="M138" t="s" s="2">
-        <v>165</v>
-      </c>
-      <c r="N138" s="2"/>
+        <v>539</v>
+      </c>
+      <c r="N138" t="s" s="2">
+        <v>584</v>
+      </c>
       <c r="O138" s="2"/>
       <c r="P138" t="s" s="2">
         <v>71</v>
@@ -16431,31 +16439,29 @@
         <v>71</v>
       </c>
       <c r="AF138" t="s" s="2">
-        <v>168</v>
+        <v>153</v>
       </c>
       <c r="AG138" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AH138" t="s" s="2">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="AI138" t="s" s="2">
         <v>90</v>
       </c>
       <c r="AJ138" t="s" s="2">
-        <v>91</v>
+        <v>131</v>
       </c>
     </row>
     <row r="139" hidden="true">
       <c r="A139" t="s" s="2">
-        <v>587</v>
+        <v>585</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>529</v>
-      </c>
-      <c r="C139" t="s" s="2">
-        <v>588</v>
-      </c>
+        <v>542</v>
+      </c>
+      <c r="C139" s="2"/>
       <c r="D139" t="s" s="2">
         <v>71</v>
       </c>
@@ -16476,17 +16482,15 @@
         <v>71</v>
       </c>
       <c r="K139" t="s" s="2">
-        <v>123</v>
+        <v>146</v>
       </c>
       <c r="L139" t="s" s="2">
-        <v>589</v>
+        <v>147</v>
       </c>
       <c r="M139" t="s" s="2">
-        <v>533</v>
-      </c>
-      <c r="N139" t="s" s="2">
-        <v>590</v>
-      </c>
+        <v>148</v>
+      </c>
+      <c r="N139" s="2"/>
       <c r="O139" s="2"/>
       <c r="P139" t="s" s="2">
         <v>71</v>
@@ -16535,27 +16539,27 @@
         <v>71</v>
       </c>
       <c r="AF139" t="s" s="2">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="AG139" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AH139" t="s" s="2">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="AI139" t="s" s="2">
-        <v>90</v>
+        <v>71</v>
       </c>
       <c r="AJ139" t="s" s="2">
-        <v>131</v>
+        <v>71</v>
       </c>
     </row>
     <row r="140" hidden="true">
       <c r="A140" t="s" s="2">
-        <v>591</v>
+        <v>586</v>
       </c>
       <c r="B140" t="s" s="2">
-        <v>536</v>
+        <v>544</v>
       </c>
       <c r="C140" s="2"/>
       <c r="D140" t="s" s="2">
@@ -16566,7 +16570,7 @@
         <v>72</v>
       </c>
       <c r="G140" t="s" s="2">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="H140" t="s" s="2">
         <v>71</v>
@@ -16578,13 +16582,13 @@
         <v>71</v>
       </c>
       <c r="K140" t="s" s="2">
-        <v>146</v>
+        <v>123</v>
       </c>
       <c r="L140" t="s" s="2">
-        <v>147</v>
+        <v>545</v>
       </c>
       <c r="M140" t="s" s="2">
-        <v>148</v>
+        <v>539</v>
       </c>
       <c r="N140" s="2"/>
       <c r="O140" s="2"/>
@@ -16623,39 +16627,39 @@
         <v>71</v>
       </c>
       <c r="AB140" t="s" s="2">
-        <v>71</v>
+        <v>127</v>
       </c>
       <c r="AC140" t="s" s="2">
-        <v>71</v>
+        <v>128</v>
       </c>
       <c r="AD140" t="s" s="2">
         <v>71</v>
       </c>
       <c r="AE140" t="s" s="2">
-        <v>71</v>
+        <v>129</v>
       </c>
       <c r="AF140" t="s" s="2">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="AG140" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AH140" t="s" s="2">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="AI140" t="s" s="2">
-        <v>71</v>
+        <v>90</v>
       </c>
       <c r="AJ140" t="s" s="2">
-        <v>71</v>
+        <v>131</v>
       </c>
     </row>
     <row r="141" hidden="true">
       <c r="A141" t="s" s="2">
-        <v>592</v>
+        <v>587</v>
       </c>
       <c r="B141" t="s" s="2">
-        <v>538</v>
+        <v>547</v>
       </c>
       <c r="C141" s="2"/>
       <c r="D141" t="s" s="2">
@@ -16663,10 +16667,10 @@
       </c>
       <c r="E141" s="2"/>
       <c r="F141" t="s" s="2">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="G141" t="s" s="2">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="H141" t="s" s="2">
         <v>71</v>
@@ -16678,22 +16682,24 @@
         <v>71</v>
       </c>
       <c r="K141" t="s" s="2">
-        <v>123</v>
+        <v>93</v>
       </c>
       <c r="L141" t="s" s="2">
-        <v>539</v>
+        <v>156</v>
       </c>
       <c r="M141" t="s" s="2">
-        <v>533</v>
-      </c>
-      <c r="N141" s="2"/>
+        <v>157</v>
+      </c>
+      <c r="N141" t="s" s="2">
+        <v>158</v>
+      </c>
       <c r="O141" s="2"/>
       <c r="P141" t="s" s="2">
         <v>71</v>
       </c>
       <c r="Q141" s="2"/>
       <c r="R141" t="s" s="2">
-        <v>71</v>
+        <v>582</v>
       </c>
       <c r="S141" t="s" s="2">
         <v>71</v>
@@ -16723,39 +16729,39 @@
         <v>71</v>
       </c>
       <c r="AB141" t="s" s="2">
-        <v>127</v>
+        <v>71</v>
       </c>
       <c r="AC141" t="s" s="2">
-        <v>128</v>
+        <v>71</v>
       </c>
       <c r="AD141" t="s" s="2">
         <v>71</v>
       </c>
       <c r="AE141" t="s" s="2">
-        <v>129</v>
+        <v>71</v>
       </c>
       <c r="AF141" t="s" s="2">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="AG141" t="s" s="2">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="AH141" t="s" s="2">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="AI141" t="s" s="2">
-        <v>90</v>
+        <v>71</v>
       </c>
       <c r="AJ141" t="s" s="2">
-        <v>131</v>
+        <v>71</v>
       </c>
     </row>
     <row r="142" hidden="true">
       <c r="A142" t="s" s="2">
-        <v>593</v>
+        <v>588</v>
       </c>
       <c r="B142" t="s" s="2">
-        <v>541</v>
+        <v>549</v>
       </c>
       <c r="C142" s="2"/>
       <c r="D142" t="s" s="2">
@@ -16763,7 +16769,7 @@
       </c>
       <c r="E142" s="2"/>
       <c r="F142" t="s" s="2">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="G142" t="s" s="2">
         <v>78</v>
@@ -16778,24 +16784,22 @@
         <v>71</v>
       </c>
       <c r="K142" t="s" s="2">
-        <v>93</v>
+        <v>262</v>
       </c>
       <c r="L142" t="s" s="2">
-        <v>156</v>
+        <v>164</v>
       </c>
       <c r="M142" t="s" s="2">
-        <v>157</v>
-      </c>
-      <c r="N142" t="s" s="2">
-        <v>158</v>
-      </c>
+        <v>165</v>
+      </c>
+      <c r="N142" s="2"/>
       <c r="O142" s="2"/>
       <c r="P142" t="s" s="2">
         <v>71</v>
       </c>
       <c r="Q142" s="2"/>
       <c r="R142" t="s" s="2">
-        <v>588</v>
+        <v>71</v>
       </c>
       <c r="S142" t="s" s="2">
         <v>71</v>
@@ -16837,29 +16841,31 @@
         <v>71</v>
       </c>
       <c r="AF142" t="s" s="2">
-        <v>160</v>
+        <v>168</v>
       </c>
       <c r="AG142" t="s" s="2">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="AH142" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AI142" t="s" s="2">
-        <v>71</v>
+        <v>90</v>
       </c>
       <c r="AJ142" t="s" s="2">
-        <v>71</v>
+        <v>91</v>
       </c>
     </row>
     <row r="143" hidden="true">
       <c r="A143" t="s" s="2">
-        <v>594</v>
+        <v>589</v>
       </c>
       <c r="B143" t="s" s="2">
-        <v>543</v>
-      </c>
-      <c r="C143" s="2"/>
+        <v>535</v>
+      </c>
+      <c r="C143" t="s" s="2">
+        <v>590</v>
+      </c>
       <c r="D143" t="s" s="2">
         <v>71</v>
       </c>
@@ -16880,15 +16886,17 @@
         <v>71</v>
       </c>
       <c r="K143" t="s" s="2">
-        <v>262</v>
+        <v>123</v>
       </c>
       <c r="L143" t="s" s="2">
-        <v>164</v>
+        <v>591</v>
       </c>
       <c r="M143" t="s" s="2">
-        <v>165</v>
-      </c>
-      <c r="N143" s="2"/>
+        <v>539</v>
+      </c>
+      <c r="N143" t="s" s="2">
+        <v>592</v>
+      </c>
       <c r="O143" s="2"/>
       <c r="P143" t="s" s="2">
         <v>71</v>
@@ -16937,27 +16945,27 @@
         <v>71</v>
       </c>
       <c r="AF143" t="s" s="2">
-        <v>168</v>
+        <v>153</v>
       </c>
       <c r="AG143" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AH143" t="s" s="2">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="AI143" t="s" s="2">
         <v>90</v>
       </c>
       <c r="AJ143" t="s" s="2">
-        <v>91</v>
+        <v>131</v>
       </c>
     </row>
     <row r="144" hidden="true">
       <c r="A144" t="s" s="2">
-        <v>595</v>
+        <v>593</v>
       </c>
       <c r="B144" t="s" s="2">
-        <v>596</v>
+        <v>542</v>
       </c>
       <c r="C144" s="2"/>
       <c r="D144" t="s" s="2">
@@ -16965,7 +16973,7 @@
       </c>
       <c r="E144" s="2"/>
       <c r="F144" t="s" s="2">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="G144" t="s" s="2">
         <v>78</v>
@@ -16980,24 +16988,22 @@
         <v>71</v>
       </c>
       <c r="K144" t="s" s="2">
-        <v>93</v>
+        <v>146</v>
       </c>
       <c r="L144" t="s" s="2">
-        <v>156</v>
+        <v>147</v>
       </c>
       <c r="M144" t="s" s="2">
-        <v>157</v>
-      </c>
-      <c r="N144" t="s" s="2">
-        <v>158</v>
-      </c>
+        <v>148</v>
+      </c>
+      <c r="N144" s="2"/>
       <c r="O144" s="2"/>
       <c r="P144" t="s" s="2">
         <v>71</v>
       </c>
       <c r="Q144" s="2"/>
       <c r="R144" t="s" s="2">
-        <v>597</v>
+        <v>71</v>
       </c>
       <c r="S144" t="s" s="2">
         <v>71</v>
@@ -17039,10 +17045,10 @@
         <v>71</v>
       </c>
       <c r="AF144" t="s" s="2">
-        <v>160</v>
+        <v>149</v>
       </c>
       <c r="AG144" t="s" s="2">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="AH144" t="s" s="2">
         <v>78</v>
@@ -17056,10 +17062,10 @@
     </row>
     <row r="145" hidden="true">
       <c r="A145" t="s" s="2">
-        <v>598</v>
+        <v>594</v>
       </c>
       <c r="B145" t="s" s="2">
-        <v>599</v>
+        <v>544</v>
       </c>
       <c r="C145" s="2"/>
       <c r="D145" t="s" s="2">
@@ -17082,13 +17088,13 @@
         <v>71</v>
       </c>
       <c r="K145" t="s" s="2">
-        <v>600</v>
+        <v>123</v>
       </c>
       <c r="L145" t="s" s="2">
-        <v>164</v>
+        <v>545</v>
       </c>
       <c r="M145" t="s" s="2">
-        <v>165</v>
+        <v>539</v>
       </c>
       <c r="N145" s="2"/>
       <c r="O145" s="2"/>
@@ -17127,39 +17133,39 @@
         <v>71</v>
       </c>
       <c r="AB145" t="s" s="2">
-        <v>71</v>
+        <v>127</v>
       </c>
       <c r="AC145" t="s" s="2">
-        <v>71</v>
+        <v>128</v>
       </c>
       <c r="AD145" t="s" s="2">
         <v>71</v>
       </c>
       <c r="AE145" t="s" s="2">
-        <v>71</v>
+        <v>129</v>
       </c>
       <c r="AF145" t="s" s="2">
-        <v>168</v>
+        <v>153</v>
       </c>
       <c r="AG145" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AH145" t="s" s="2">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="AI145" t="s" s="2">
         <v>90</v>
       </c>
       <c r="AJ145" t="s" s="2">
-        <v>91</v>
+        <v>131</v>
       </c>
     </row>
     <row r="146" hidden="true">
       <c r="A146" t="s" s="2">
-        <v>601</v>
+        <v>595</v>
       </c>
       <c r="B146" t="s" s="2">
-        <v>602</v>
+        <v>547</v>
       </c>
       <c r="C146" s="2"/>
       <c r="D146" t="s" s="2">
@@ -17179,19 +17185,19 @@
         <v>71</v>
       </c>
       <c r="J146" t="s" s="2">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="K146" t="s" s="2">
-        <v>99</v>
+        <v>93</v>
       </c>
       <c r="L146" t="s" s="2">
-        <v>413</v>
+        <v>156</v>
       </c>
       <c r="M146" t="s" s="2">
-        <v>414</v>
+        <v>157</v>
       </c>
       <c r="N146" t="s" s="2">
-        <v>316</v>
+        <v>158</v>
       </c>
       <c r="O146" s="2"/>
       <c r="P146" t="s" s="2">
@@ -17199,10 +17205,10 @@
       </c>
       <c r="Q146" s="2"/>
       <c r="R146" t="s" s="2">
-        <v>71</v>
+        <v>590</v>
       </c>
       <c r="S146" t="s" s="2">
-        <v>603</v>
+        <v>71</v>
       </c>
       <c r="T146" t="s" s="2">
         <v>71</v>
@@ -17217,13 +17223,13 @@
         <v>71</v>
       </c>
       <c r="X146" t="s" s="2">
-        <v>220</v>
+        <v>71</v>
       </c>
       <c r="Y146" t="s" s="2">
-        <v>416</v>
+        <v>71</v>
       </c>
       <c r="Z146" t="s" s="2">
-        <v>417</v>
+        <v>71</v>
       </c>
       <c r="AA146" t="s" s="2">
         <v>71</v>
@@ -17241,27 +17247,27 @@
         <v>71</v>
       </c>
       <c r="AF146" t="s" s="2">
-        <v>418</v>
+        <v>160</v>
       </c>
       <c r="AG146" t="s" s="2">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="AH146" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AI146" t="s" s="2">
-        <v>419</v>
+        <v>71</v>
       </c>
       <c r="AJ146" t="s" s="2">
-        <v>91</v>
+        <v>71</v>
       </c>
     </row>
     <row r="147" hidden="true">
       <c r="A147" t="s" s="2">
-        <v>604</v>
+        <v>596</v>
       </c>
       <c r="B147" t="s" s="2">
-        <v>605</v>
+        <v>549</v>
       </c>
       <c r="C147" s="2"/>
       <c r="D147" t="s" s="2">
@@ -17269,35 +17275,31 @@
       </c>
       <c r="E147" s="2"/>
       <c r="F147" t="s" s="2">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="G147" t="s" s="2">
         <v>78</v>
       </c>
       <c r="H147" t="s" s="2">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="I147" t="s" s="2">
         <v>71</v>
       </c>
       <c r="J147" t="s" s="2">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="K147" t="s" s="2">
-        <v>146</v>
+        <v>262</v>
       </c>
       <c r="L147" t="s" s="2">
-        <v>606</v>
+        <v>164</v>
       </c>
       <c r="M147" t="s" s="2">
-        <v>422</v>
-      </c>
-      <c r="N147" t="s" s="2">
-        <v>423</v>
-      </c>
-      <c r="O147" t="s" s="2">
-        <v>424</v>
-      </c>
+        <v>165</v>
+      </c>
+      <c r="N147" s="2"/>
+      <c r="O147" s="2"/>
       <c r="P147" t="s" s="2">
         <v>71</v>
       </c>
@@ -17345,7 +17347,7 @@
         <v>71</v>
       </c>
       <c r="AF147" t="s" s="2">
-        <v>425</v>
+        <v>168</v>
       </c>
       <c r="AG147" t="s" s="2">
         <v>72</v>
@@ -17362,10 +17364,10 @@
     </row>
     <row r="148" hidden="true">
       <c r="A148" t="s" s="2">
-        <v>607</v>
+        <v>597</v>
       </c>
       <c r="B148" t="s" s="2">
-        <v>608</v>
+        <v>598</v>
       </c>
       <c r="C148" s="2"/>
       <c r="D148" t="s" s="2">
@@ -17373,7 +17375,7 @@
       </c>
       <c r="E148" s="2"/>
       <c r="F148" t="s" s="2">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="G148" t="s" s="2">
         <v>78</v>
@@ -17382,32 +17384,30 @@
         <v>71</v>
       </c>
       <c r="I148" t="s" s="2">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="J148" t="s" s="2">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="K148" t="s" s="2">
-        <v>99</v>
+        <v>93</v>
       </c>
       <c r="L148" t="s" s="2">
-        <v>427</v>
+        <v>156</v>
       </c>
       <c r="M148" t="s" s="2">
-        <v>428</v>
+        <v>157</v>
       </c>
       <c r="N148" t="s" s="2">
-        <v>609</v>
-      </c>
-      <c r="O148" t="s" s="2">
-        <v>430</v>
-      </c>
+        <v>158</v>
+      </c>
+      <c r="O148" s="2"/>
       <c r="P148" t="s" s="2">
         <v>71</v>
       </c>
       <c r="Q148" s="2"/>
       <c r="R148" t="s" s="2">
-        <v>71</v>
+        <v>599</v>
       </c>
       <c r="S148" t="s" s="2">
         <v>71</v>
@@ -17425,13 +17425,13 @@
         <v>71</v>
       </c>
       <c r="X148" t="s" s="2">
-        <v>220</v>
+        <v>71</v>
       </c>
       <c r="Y148" t="s" s="2">
-        <v>431</v>
+        <v>71</v>
       </c>
       <c r="Z148" t="s" s="2">
-        <v>432</v>
+        <v>71</v>
       </c>
       <c r="AA148" t="s" s="2">
         <v>71</v>
@@ -17449,27 +17449,27 @@
         <v>71</v>
       </c>
       <c r="AF148" t="s" s="2">
-        <v>433</v>
+        <v>160</v>
       </c>
       <c r="AG148" t="s" s="2">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="AH148" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AI148" t="s" s="2">
-        <v>90</v>
+        <v>71</v>
       </c>
       <c r="AJ148" t="s" s="2">
-        <v>91</v>
+        <v>71</v>
       </c>
     </row>
     <row r="149" hidden="true">
       <c r="A149" t="s" s="2">
-        <v>610</v>
+        <v>600</v>
       </c>
       <c r="B149" t="s" s="2">
-        <v>611</v>
+        <v>601</v>
       </c>
       <c r="C149" s="2"/>
       <c r="D149" t="s" s="2">
@@ -17480,7 +17480,7 @@
         <v>72</v>
       </c>
       <c r="G149" t="s" s="2">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="H149" t="s" s="2">
         <v>71</v>
@@ -17489,20 +17489,18 @@
         <v>71</v>
       </c>
       <c r="J149" t="s" s="2">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="K149" t="s" s="2">
-        <v>435</v>
+        <v>602</v>
       </c>
       <c r="L149" t="s" s="2">
-        <v>436</v>
+        <v>164</v>
       </c>
       <c r="M149" t="s" s="2">
-        <v>437</v>
-      </c>
-      <c r="N149" t="s" s="2">
-        <v>438</v>
-      </c>
+        <v>165</v>
+      </c>
+      <c r="N149" s="2"/>
       <c r="O149" s="2"/>
       <c r="P149" t="s" s="2">
         <v>71</v>
@@ -17551,7 +17549,7 @@
         <v>71</v>
       </c>
       <c r="AF149" t="s" s="2">
-        <v>439</v>
+        <v>168</v>
       </c>
       <c r="AG149" t="s" s="2">
         <v>72</v>
@@ -17568,10 +17566,10 @@
     </row>
     <row r="150" hidden="true">
       <c r="A150" t="s" s="2">
-        <v>612</v>
+        <v>603</v>
       </c>
       <c r="B150" t="s" s="2">
-        <v>613</v>
+        <v>604</v>
       </c>
       <c r="C150" s="2"/>
       <c r="D150" t="s" s="2">
@@ -17579,7 +17577,7 @@
       </c>
       <c r="E150" s="2"/>
       <c r="F150" t="s" s="2">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="G150" t="s" s="2">
         <v>78</v>
@@ -17594,16 +17592,16 @@
         <v>79</v>
       </c>
       <c r="K150" t="s" s="2">
-        <v>163</v>
+        <v>99</v>
       </c>
       <c r="L150" t="s" s="2">
-        <v>441</v>
+        <v>413</v>
       </c>
       <c r="M150" t="s" s="2">
-        <v>442</v>
+        <v>414</v>
       </c>
       <c r="N150" t="s" s="2">
-        <v>251</v>
+        <v>316</v>
       </c>
       <c r="O150" s="2"/>
       <c r="P150" t="s" s="2">
@@ -17614,7 +17612,7 @@
         <v>71</v>
       </c>
       <c r="S150" t="s" s="2">
-        <v>71</v>
+        <v>605</v>
       </c>
       <c r="T150" t="s" s="2">
         <v>71</v>
@@ -17629,13 +17627,13 @@
         <v>71</v>
       </c>
       <c r="X150" t="s" s="2">
-        <v>71</v>
+        <v>220</v>
       </c>
       <c r="Y150" t="s" s="2">
-        <v>71</v>
+        <v>416</v>
       </c>
       <c r="Z150" t="s" s="2">
-        <v>71</v>
+        <v>417</v>
       </c>
       <c r="AA150" t="s" s="2">
         <v>71</v>
@@ -17653,7 +17651,7 @@
         <v>71</v>
       </c>
       <c r="AF150" t="s" s="2">
-        <v>444</v>
+        <v>418</v>
       </c>
       <c r="AG150" t="s" s="2">
         <v>72</v>
@@ -17662,18 +17660,18 @@
         <v>78</v>
       </c>
       <c r="AI150" t="s" s="2">
-        <v>90</v>
+        <v>419</v>
       </c>
       <c r="AJ150" t="s" s="2">
-        <v>253</v>
+        <v>91</v>
       </c>
     </row>
     <row r="151" hidden="true">
       <c r="A151" t="s" s="2">
-        <v>614</v>
+        <v>606</v>
       </c>
       <c r="B151" t="s" s="2">
-        <v>614</v>
+        <v>607</v>
       </c>
       <c r="C151" s="2"/>
       <c r="D151" t="s" s="2">
@@ -17681,34 +17679,34 @@
       </c>
       <c r="E151" s="2"/>
       <c r="F151" t="s" s="2">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="G151" t="s" s="2">
         <v>78</v>
       </c>
       <c r="H151" t="s" s="2">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="I151" t="s" s="2">
         <v>71</v>
       </c>
       <c r="J151" t="s" s="2">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="K151" t="s" s="2">
-        <v>615</v>
+        <v>146</v>
       </c>
       <c r="L151" t="s" s="2">
-        <v>616</v>
+        <v>608</v>
       </c>
       <c r="M151" t="s" s="2">
-        <v>448</v>
+        <v>422</v>
       </c>
       <c r="N151" t="s" s="2">
-        <v>617</v>
+        <v>423</v>
       </c>
       <c r="O151" t="s" s="2">
-        <v>618</v>
+        <v>424</v>
       </c>
       <c r="P151" t="s" s="2">
         <v>71</v>
@@ -17757,7 +17755,7 @@
         <v>71</v>
       </c>
       <c r="AF151" t="s" s="2">
-        <v>614</v>
+        <v>425</v>
       </c>
       <c r="AG151" t="s" s="2">
         <v>72</v>
@@ -17774,10 +17772,10 @@
     </row>
     <row r="152" hidden="true">
       <c r="A152" t="s" s="2">
-        <v>619</v>
+        <v>609</v>
       </c>
       <c r="B152" t="s" s="2">
-        <v>619</v>
+        <v>610</v>
       </c>
       <c r="C152" s="2"/>
       <c r="D152" t="s" s="2">
@@ -17788,31 +17786,31 @@
         <v>72</v>
       </c>
       <c r="G152" t="s" s="2">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="H152" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="I152" t="s" s="2">
         <v>79</v>
       </c>
-      <c r="I152" t="s" s="2">
-        <v>71</v>
-      </c>
       <c r="J152" t="s" s="2">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="K152" t="s" s="2">
-        <v>620</v>
+        <v>99</v>
       </c>
       <c r="L152" t="s" s="2">
-        <v>621</v>
+        <v>427</v>
       </c>
       <c r="M152" t="s" s="2">
-        <v>622</v>
+        <v>428</v>
       </c>
       <c r="N152" t="s" s="2">
-        <v>623</v>
+        <v>611</v>
       </c>
       <c r="O152" t="s" s="2">
-        <v>624</v>
+        <v>430</v>
       </c>
       <c r="P152" t="s" s="2">
         <v>71</v>
@@ -17837,13 +17835,13 @@
         <v>71</v>
       </c>
       <c r="X152" t="s" s="2">
-        <v>71</v>
+        <v>220</v>
       </c>
       <c r="Y152" t="s" s="2">
-        <v>71</v>
+        <v>431</v>
       </c>
       <c r="Z152" t="s" s="2">
-        <v>71</v>
+        <v>432</v>
       </c>
       <c r="AA152" t="s" s="2">
         <v>71</v>
@@ -17861,23 +17859,435 @@
         <v>71</v>
       </c>
       <c r="AF152" t="s" s="2">
-        <v>619</v>
+        <v>433</v>
       </c>
       <c r="AG152" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AH152" t="s" s="2">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="AI152" t="s" s="2">
         <v>90</v>
       </c>
       <c r="AJ152" t="s" s="2">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="153" hidden="true">
+      <c r="A153" t="s" s="2">
+        <v>612</v>
+      </c>
+      <c r="B153" t="s" s="2">
+        <v>613</v>
+      </c>
+      <c r="C153" s="2"/>
+      <c r="D153" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="E153" s="2"/>
+      <c r="F153" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="G153" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H153" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="I153" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="J153" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="K153" t="s" s="2">
+        <v>435</v>
+      </c>
+      <c r="L153" t="s" s="2">
+        <v>436</v>
+      </c>
+      <c r="M153" t="s" s="2">
+        <v>437</v>
+      </c>
+      <c r="N153" t="s" s="2">
+        <v>438</v>
+      </c>
+      <c r="O153" s="2"/>
+      <c r="P153" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="Q153" s="2"/>
+      <c r="R153" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="S153" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="T153" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="U153" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="V153" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="W153" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="X153" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="Y153" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="Z153" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="AA153" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="AB153" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="AC153" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="AD153" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="AE153" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="AF153" t="s" s="2">
+        <v>439</v>
+      </c>
+      <c r="AG153" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AH153" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI153" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AJ153" t="s" s="2">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="154" hidden="true">
+      <c r="A154" t="s" s="2">
+        <v>614</v>
+      </c>
+      <c r="B154" t="s" s="2">
+        <v>615</v>
+      </c>
+      <c r="C154" s="2"/>
+      <c r="D154" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="E154" s="2"/>
+      <c r="F154" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="G154" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H154" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="I154" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="J154" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="K154" t="s" s="2">
+        <v>163</v>
+      </c>
+      <c r="L154" t="s" s="2">
+        <v>441</v>
+      </c>
+      <c r="M154" t="s" s="2">
+        <v>442</v>
+      </c>
+      <c r="N154" t="s" s="2">
+        <v>443</v>
+      </c>
+      <c r="O154" s="2"/>
+      <c r="P154" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="Q154" s="2"/>
+      <c r="R154" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="S154" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="T154" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="U154" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="V154" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="W154" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="X154" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="Y154" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="Z154" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="AA154" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="AB154" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="AC154" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="AD154" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="AE154" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="AF154" t="s" s="2">
+        <v>444</v>
+      </c>
+      <c r="AG154" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AH154" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI154" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AJ154" t="s" s="2">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="155" hidden="true">
+      <c r="A155" t="s" s="2">
+        <v>616</v>
+      </c>
+      <c r="B155" t="s" s="2">
+        <v>616</v>
+      </c>
+      <c r="C155" s="2"/>
+      <c r="D155" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="E155" s="2"/>
+      <c r="F155" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="G155" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H155" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="I155" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="J155" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="K155" t="s" s="2">
+        <v>617</v>
+      </c>
+      <c r="L155" t="s" s="2">
+        <v>618</v>
+      </c>
+      <c r="M155" t="s" s="2">
+        <v>454</v>
+      </c>
+      <c r="N155" t="s" s="2">
+        <v>619</v>
+      </c>
+      <c r="O155" t="s" s="2">
+        <v>620</v>
+      </c>
+      <c r="P155" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="Q155" s="2"/>
+      <c r="R155" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="S155" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="T155" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="U155" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="V155" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="W155" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="X155" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="Y155" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="Z155" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="AA155" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="AB155" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="AC155" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="AD155" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="AE155" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="AF155" t="s" s="2">
+        <v>616</v>
+      </c>
+      <c r="AG155" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AH155" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI155" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AJ155" t="s" s="2">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="156" hidden="true">
+      <c r="A156" t="s" s="2">
+        <v>621</v>
+      </c>
+      <c r="B156" t="s" s="2">
+        <v>621</v>
+      </c>
+      <c r="C156" s="2"/>
+      <c r="D156" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="E156" s="2"/>
+      <c r="F156" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="G156" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="H156" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="I156" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="J156" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="K156" t="s" s="2">
+        <v>622</v>
+      </c>
+      <c r="L156" t="s" s="2">
+        <v>623</v>
+      </c>
+      <c r="M156" t="s" s="2">
+        <v>624</v>
+      </c>
+      <c r="N156" t="s" s="2">
+        <v>625</v>
+      </c>
+      <c r="O156" t="s" s="2">
+        <v>626</v>
+      </c>
+      <c r="P156" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="Q156" s="2"/>
+      <c r="R156" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="S156" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="T156" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="U156" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="V156" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="W156" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="X156" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="Y156" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="Z156" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="AA156" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="AB156" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="AC156" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="AD156" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="AE156" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="AF156" t="s" s="2">
+        <v>621</v>
+      </c>
+      <c r="AG156" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AH156" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AI156" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AJ156" t="s" s="2">
         <v>260</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AJ152">
+  <autoFilter ref="A1:AJ156">
     <filterColumn colId="6">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -17887,7 +18297,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI151">
+  <conditionalFormatting sqref="A2:AI155">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/ig/mc-add-profils-dp/StructureDefinition-as-dp-organization.xlsx
+++ b/ig/mc-add-profils-dp/StructureDefinition-as-dp-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-23T08:43:56+00:00</t>
+    <t>2023-05-23T08:57:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
